--- a/output/petroleum_sale_flat_table.xlsx
+++ b/output/petroleum_sale_flat_table.xlsx
@@ -49094,4 +49094,285 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CCB40CA4B69967448E5E142573FA85FC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3f19dfd05c72a4aa217b148f0f00ef59">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e9ead7b-6342-4494-9745-aa11ca9090cb" xmlns:ns3="9e595a92-2a84-46d4-9885-e168ac7f98a1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3d61ddcb55407106f5563e5e5e5e7a99" ns2:_="" ns3:_="">
+    <xsd:import namespace="7e9ead7b-6342-4494-9745-aa11ca9090cb"/>
+    <xsd:import namespace="9e595a92-2a84-46d4-9885-e168ac7f98a1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7e9ead7b-6342-4494-9745-aa11ca9090cb" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="17" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="18" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4b3741f9-8584-47b2-968f-3f53d9bbee55" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="24" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9e595a92-2a84-46d4-9885-e168ac7f98a1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{0d5f833c-ae06-418d-979f-18c784237a1f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9e595a92-2a84-46d4-9885-e168ac7f98a1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e9ead7b-6342-4494-9745-aa11ca9090cb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9e595a92-2a84-46d4-9885-e168ac7f98a1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50007C9C-1752-4984-AA99-34BC3777D48B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A7817FA-8C46-4044-9B90-E2F88357EB95}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF204B21-1C65-4F30-B165-D4B3EFF73D32}"/>
 </file>
--- a/output/petroleum_sale_flat_table.xlsx
+++ b/output/petroleum_sale_flat_table.xlsx
@@ -36774,13 +36774,13 @@
       </c>
       <c r="O380" t="inlineStr"/>
       <c r="P380" t="n">
-        <v>1615263456.27</v>
+        <v>2088161283.13</v>
       </c>
       <c r="Q380" t="n">
-        <v>600878006.01</v>
+        <v>776795997.61</v>
       </c>
       <c r="R380" t="n">
-        <v>2648.276779745217</v>
+        <v>3423.60809130556</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
@@ -36789,10 +36789,10 @@
       </c>
       <c r="T380" t="inlineStr"/>
       <c r="U380" t="n">
-        <v>37.20000001718358</v>
+        <v>37.20000001367902</v>
       </c>
       <c r="V380" t="n">
-        <v>2648.276779745217</v>
+        <v>3423.60809130556</v>
       </c>
       <c r="W380" t="inlineStr">
         <is>
@@ -36870,13 +36870,13 @@
       </c>
       <c r="O381" t="inlineStr"/>
       <c r="P381" t="n">
-        <v>1855027713.47</v>
+        <v>2394398017.1</v>
       </c>
       <c r="Q381" t="n">
-        <v>704910531.13</v>
+        <v>909871246.47</v>
       </c>
       <c r="R381" t="n">
-        <v>2686.748248164928</v>
+        <v>3467.950711000006</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
@@ -36885,10 +36885,10 @@
       </c>
       <c r="T381" t="inlineStr"/>
       <c r="U381" t="n">
-        <v>38.00000000061455</v>
+        <v>37.99999999883061</v>
       </c>
       <c r="V381" t="n">
-        <v>2686.748248164928</v>
+        <v>3467.950711000006</v>
       </c>
       <c r="W381" t="inlineStr">
         <is>
@@ -37888,13 +37888,13 @@
       </c>
       <c r="O392" t="inlineStr"/>
       <c r="P392" t="n">
-        <v>1189489460.42</v>
+        <v>1192623612.47</v>
       </c>
       <c r="Q392" t="n">
-        <v>442490079.28</v>
+        <v>443655983.84</v>
       </c>
       <c r="R392" t="n">
-        <v>2612.499830707633</v>
+        <v>2619.383432431305</v>
       </c>
       <c r="S392" t="inlineStr">
         <is>
@@ -37903,10 +37903,10 @@
       </c>
       <c r="T392" t="inlineStr"/>
       <c r="U392" t="n">
-        <v>37.20000000031609</v>
+        <v>37.20000000009726</v>
       </c>
       <c r="V392" t="n">
-        <v>2612.499830707633</v>
+        <v>2619.383432431305</v>
       </c>
       <c r="W392" t="inlineStr">
         <is>
@@ -49094,285 +49094,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CCB40CA4B69967448E5E142573FA85FC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3f19dfd05c72a4aa217b148f0f00ef59">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e9ead7b-6342-4494-9745-aa11ca9090cb" xmlns:ns3="9e595a92-2a84-46d4-9885-e168ac7f98a1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3d61ddcb55407106f5563e5e5e5e7a99" ns2:_="" ns3:_="">
-    <xsd:import namespace="7e9ead7b-6342-4494-9745-aa11ca9090cb"/>
-    <xsd:import namespace="9e595a92-2a84-46d4-9885-e168ac7f98a1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7e9ead7b-6342-4494-9745-aa11ca9090cb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="17" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="18" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4b3741f9-8584-47b2-968f-3f53d9bbee55" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="24" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9e595a92-2a84-46d4-9885-e168ac7f98a1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{0d5f833c-ae06-418d-979f-18c784237a1f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9e595a92-2a84-46d4-9885-e168ac7f98a1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e9ead7b-6342-4494-9745-aa11ca9090cb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9e595a92-2a84-46d4-9885-e168ac7f98a1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50007C9C-1752-4984-AA99-34BC3777D48B}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A7817FA-8C46-4044-9B90-E2F88357EB95}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF204B21-1C65-4F30-B165-D4B3EFF73D32}"/>
 </file>
--- a/output/petroleum_sale_flat_table.xlsx
+++ b/output/petroleum_sale_flat_table.xlsx
@@ -36774,13 +36774,13 @@
       </c>
       <c r="O380" t="inlineStr"/>
       <c r="P380" t="n">
-        <v>2088161283.13</v>
+        <v>1615263456.27</v>
       </c>
       <c r="Q380" t="n">
-        <v>776795997.61</v>
+        <v>600878006.01</v>
       </c>
       <c r="R380" t="n">
-        <v>3423.60809130556</v>
+        <v>2648.276779745217</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
@@ -36789,10 +36789,10 @@
       </c>
       <c r="T380" t="inlineStr"/>
       <c r="U380" t="n">
-        <v>37.20000001367902</v>
+        <v>37.20000001718358</v>
       </c>
       <c r="V380" t="n">
-        <v>3423.60809130556</v>
+        <v>2648.276779745217</v>
       </c>
       <c r="W380" t="inlineStr">
         <is>
@@ -36870,13 +36870,13 @@
       </c>
       <c r="O381" t="inlineStr"/>
       <c r="P381" t="n">
-        <v>2394398017.1</v>
+        <v>1855027713.47</v>
       </c>
       <c r="Q381" t="n">
-        <v>909871246.47</v>
+        <v>704910531.13</v>
       </c>
       <c r="R381" t="n">
-        <v>3467.950711000006</v>
+        <v>2686.748248164928</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
@@ -36885,10 +36885,10 @@
       </c>
       <c r="T381" t="inlineStr"/>
       <c r="U381" t="n">
-        <v>37.99999999883061</v>
+        <v>38.00000000061455</v>
       </c>
       <c r="V381" t="n">
-        <v>3467.950711000006</v>
+        <v>2686.748248164928</v>
       </c>
       <c r="W381" t="inlineStr">
         <is>
@@ -37888,13 +37888,13 @@
       </c>
       <c r="O392" t="inlineStr"/>
       <c r="P392" t="n">
-        <v>1192623612.47</v>
+        <v>1189489460.42</v>
       </c>
       <c r="Q392" t="n">
-        <v>443655983.84</v>
+        <v>442490079.28</v>
       </c>
       <c r="R392" t="n">
-        <v>2619.383432431305</v>
+        <v>2612.499830707633</v>
       </c>
       <c r="S392" t="inlineStr">
         <is>
@@ -37903,10 +37903,10 @@
       </c>
       <c r="T392" t="inlineStr"/>
       <c r="U392" t="n">
-        <v>37.20000000009726</v>
+        <v>37.20000000031609</v>
       </c>
       <c r="V392" t="n">
-        <v>2619.383432431305</v>
+        <v>2612.499830707633</v>
       </c>
       <c r="W392" t="inlineStr">
         <is>

--- a/output/petroleum_sale_flat_table.xlsx
+++ b/output/petroleum_sale_flat_table.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB492"/>
+  <dimension ref="A1:AB559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43251,7 +43251,7 @@
         <v>1841101559.53</v>
       </c>
       <c r="Q448" t="n">
-        <v>684889772.3099999</v>
+        <v>684889780.1799999</v>
       </c>
       <c r="R448" t="n">
         <v>2615.156502346551</v>
@@ -43263,7 +43263,7 @@
       </c>
       <c r="T448" t="inlineStr"/>
       <c r="U448" t="n">
-        <v>37.19999957443086</v>
+        <v>37.20000000189234</v>
       </c>
       <c r="V448" t="n">
         <v>2615.156502346551</v>
@@ -43344,13 +43344,13 @@
       </c>
       <c r="O449" t="inlineStr"/>
       <c r="P449" t="n">
-        <v>2106751373.68</v>
+        <v>1884080051.17</v>
       </c>
       <c r="Q449" t="n">
-        <v>800565521.99</v>
+        <v>715950419.4299999</v>
       </c>
       <c r="R449" t="n">
-        <v>2925.023878731165</v>
+        <v>2615.865928919224</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
@@ -43359,10 +43359,10 @@
       </c>
       <c r="T449" t="inlineStr"/>
       <c r="U449" t="n">
-        <v>37.99999999960128</v>
+        <v>37.99999999922508</v>
       </c>
       <c r="V449" t="n">
-        <v>2925.023878731165</v>
+        <v>2615.865928919224</v>
       </c>
       <c r="W449" t="inlineStr">
         <is>
@@ -47356,6 +47356,6400 @@
         </is>
       </c>
       <c r="AB492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>8</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>G1/61</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G493" t="n">
+        <v>24042.937</v>
+      </c>
+      <c r="H493" t="n">
+        <v>24042.937</v>
+      </c>
+      <c r="I493" t="n">
+        <v>21954719</v>
+      </c>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="n">
+        <v>775.5786129032259</v>
+      </c>
+      <c r="M493" t="n">
+        <v>708216.7419354839</v>
+      </c>
+      <c r="N493" t="inlineStr"/>
+      <c r="O493" t="n">
+        <v>913.146301552094</v>
+      </c>
+      <c r="P493" t="n">
+        <v>3220208409.33</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>1197917528.28</v>
+      </c>
+      <c r="R493" t="n">
+        <v>146.6750000002277</v>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T493" t="n">
+        <v>133935.7337803613</v>
+      </c>
+      <c r="U493" t="n">
+        <v>37.20000000028693</v>
+      </c>
+      <c r="V493" t="n">
+        <v>146.6750000002277</v>
+      </c>
+      <c r="W493" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y493" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="Z493" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA493" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="AB493" t="inlineStr">
+        <is>
+          <t>เอราวัณเดิม</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>8</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>G12/48</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G494" t="n">
+        <v>125.205</v>
+      </c>
+      <c r="H494" t="n">
+        <v>125.205</v>
+      </c>
+      <c r="I494" t="n">
+        <v>122671</v>
+      </c>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="n">
+        <v>4.038870967741936</v>
+      </c>
+      <c r="M494" t="n">
+        <v>3957.129032258064</v>
+      </c>
+      <c r="N494" t="inlineStr"/>
+      <c r="O494" t="n">
+        <v>979.761191645701</v>
+      </c>
+      <c r="P494" t="n">
+        <v>33281844.48</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>1664092.22</v>
+      </c>
+      <c r="R494" t="n">
+        <v>271.3098000342379</v>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T494" t="n">
+        <v>265818.8129867018</v>
+      </c>
+      <c r="U494" t="n">
+        <v>4.999999987981435</v>
+      </c>
+      <c r="V494" t="n">
+        <v>271.3098000342379</v>
+      </c>
+      <c r="W494" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X494" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y494" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z494" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+      <c r="AA494" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB494" t="inlineStr">
+        <is>
+          <t>สงขลา</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>8</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>G2/61</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G495" t="n">
+        <v>20417.231</v>
+      </c>
+      <c r="H495" t="n">
+        <v>20417.231</v>
+      </c>
+      <c r="I495" t="n">
+        <v>19840776</v>
+      </c>
+      <c r="J495" t="inlineStr"/>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="n">
+        <v>658.6203548387097</v>
+      </c>
+      <c r="M495" t="n">
+        <v>640025.0322580645</v>
+      </c>
+      <c r="N495" t="inlineStr"/>
+      <c r="O495" t="n">
+        <v>971.7662497916589</v>
+      </c>
+      <c r="P495" t="n">
+        <v>2910145819.8</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>1105855411.52</v>
+      </c>
+      <c r="R495" t="n">
+        <v>146.675</v>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T495" t="n">
+        <v>142533.8146881916</v>
+      </c>
+      <c r="U495" t="n">
+        <v>37.99999999986255</v>
+      </c>
+      <c r="V495" t="n">
+        <v>146.675</v>
+      </c>
+      <c r="W495" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X495" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y495" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="Z495" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA495" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="AB495" t="inlineStr">
+        <is>
+          <t>บงกชเดิม</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>8</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>ชบา</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G496" t="n">
+        <v>3.9363</v>
+      </c>
+      <c r="H496" t="n">
+        <v>3.9363</v>
+      </c>
+      <c r="I496" t="n">
+        <v>3046</v>
+      </c>
+      <c r="J496" t="inlineStr"/>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="n">
+        <v>0.1269774193548387</v>
+      </c>
+      <c r="M496" t="n">
+        <v>98.25806451612904</v>
+      </c>
+      <c r="N496" t="inlineStr"/>
+      <c r="O496" t="n">
+        <v>773.8231333993851</v>
+      </c>
+      <c r="P496" t="n">
+        <v>673732.86</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>70066.67999999999</v>
+      </c>
+      <c r="R496" t="n">
+        <v>221.1860998030203</v>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T496" t="n">
+        <v>171158.9208139624</v>
+      </c>
+      <c r="U496" t="n">
+        <v>10.39977180272905</v>
+      </c>
+      <c r="V496" t="n">
+        <v>221.1860998030203</v>
+      </c>
+      <c r="W496" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X496" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y496" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z496" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA496" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>8</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>ตราด</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G497" t="n">
+        <v>21.5281</v>
+      </c>
+      <c r="H497" t="n">
+        <v>21.5281</v>
+      </c>
+      <c r="I497" t="n">
+        <v>20724</v>
+      </c>
+      <c r="J497" t="inlineStr"/>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="n">
+        <v>0.6944548387096774</v>
+      </c>
+      <c r="M497" t="n">
+        <v>668.516129032258</v>
+      </c>
+      <c r="N497" t="inlineStr"/>
+      <c r="O497" t="n">
+        <v>962.6488171273825</v>
+      </c>
+      <c r="P497" t="n">
+        <v>4097151.38</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>512143.92</v>
+      </c>
+      <c r="R497" t="n">
+        <v>197.7008000386026</v>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T497" t="n">
+        <v>190316.4413022979</v>
+      </c>
+      <c r="U497" t="n">
+        <v>12.499999938982</v>
+      </c>
+      <c r="V497" t="n">
+        <v>197.7008000386026</v>
+      </c>
+      <c r="W497" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X497" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y497" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z497" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA497" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>8</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>ตราด_11A</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G498" t="n">
+        <v>5.3304</v>
+      </c>
+      <c r="H498" t="n">
+        <v>5.3304</v>
+      </c>
+      <c r="I498" t="n">
+        <v>5519.064</v>
+      </c>
+      <c r="J498" t="inlineStr"/>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="n">
+        <v>0.1719483870967742</v>
+      </c>
+      <c r="M498" t="n">
+        <v>178.0343225806452</v>
+      </c>
+      <c r="N498" t="inlineStr"/>
+      <c r="O498" t="n">
+        <v>1035.393966681675</v>
+      </c>
+      <c r="P498" t="n">
+        <v>1091123.37</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>136390.42</v>
+      </c>
+      <c r="R498" t="n">
+        <v>197.7008003531034</v>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T498" t="n">
+        <v>204698.2158937416</v>
+      </c>
+      <c r="U498" t="n">
+        <v>12.49999988543917</v>
+      </c>
+      <c r="V498" t="n">
+        <v>197.7008003531034</v>
+      </c>
+      <c r="W498" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X498" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y498" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z498" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA498" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>8</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>น้ำพอง</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G499" t="n">
+        <v>168.3958</v>
+      </c>
+      <c r="H499" t="n">
+        <v>168.3958</v>
+      </c>
+      <c r="I499" t="n">
+        <v>162193</v>
+      </c>
+      <c r="J499" t="inlineStr"/>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="n">
+        <v>5.432122580645162</v>
+      </c>
+      <c r="M499" t="n">
+        <v>5232.032258064516</v>
+      </c>
+      <c r="N499" t="inlineStr"/>
+      <c r="O499" t="n">
+        <v>963.1653521049811</v>
+      </c>
+      <c r="P499" t="n">
+        <v>38113116.74</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>4764139.59</v>
+      </c>
+      <c r="R499" t="n">
+        <v>234.9862000209627</v>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T499" t="n">
+        <v>226330.5660830021</v>
+      </c>
+      <c r="U499" t="n">
+        <v>12.49999999344058</v>
+      </c>
+      <c r="V499" t="n">
+        <v>234.9862000209627</v>
+      </c>
+      <c r="W499" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X499" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y499" t="inlineStr">
+        <is>
+          <t>MH Energy</t>
+        </is>
+      </c>
+      <c r="Z499" t="inlineStr">
+        <is>
+          <t>โคราช</t>
+        </is>
+      </c>
+      <c r="AA499" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>8</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>บูรพา</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G500" t="n">
+        <v>2.6255</v>
+      </c>
+      <c r="H500" t="n">
+        <v>2.6255</v>
+      </c>
+      <c r="I500" t="n">
+        <v>4578.306</v>
+      </c>
+      <c r="J500" t="inlineStr"/>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="n">
+        <v>0.08469354838709678</v>
+      </c>
+      <c r="M500" t="n">
+        <v>147.6872903225806</v>
+      </c>
+      <c r="N500" t="inlineStr"/>
+      <c r="O500" t="n">
+        <v>1743.784422014854</v>
+      </c>
+      <c r="P500" t="n">
+        <v>234775.53</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>11738.78</v>
+      </c>
+      <c r="R500" t="n">
+        <v>51.27999963305206</v>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T500" t="n">
+        <v>89421.2645210436</v>
+      </c>
+      <c r="U500" t="n">
+        <v>5.000001490785689</v>
+      </c>
+      <c r="V500" t="n">
+        <v>51.27999963305206</v>
+      </c>
+      <c r="W500" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y500" t="inlineStr">
+        <is>
+          <t>UAC Utilities</t>
+        </is>
+      </c>
+      <c r="Z500" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="AA500" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>8</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>มรกต</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G501" t="n">
+        <v>4992.7008</v>
+      </c>
+      <c r="H501" t="n">
+        <v>4992.7008</v>
+      </c>
+      <c r="I501" t="n">
+        <v>4898279</v>
+      </c>
+      <c r="J501" t="inlineStr"/>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="n">
+        <v>161.054864516129</v>
+      </c>
+      <c r="M501" t="n">
+        <v>158009</v>
+      </c>
+      <c r="N501" t="inlineStr"/>
+      <c r="O501" t="n">
+        <v>981.088031551981</v>
+      </c>
+      <c r="P501" t="n">
+        <v>1128297015.23</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>141037126.9</v>
+      </c>
+      <c r="R501" t="n">
+        <v>230.3456000015516</v>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T501" t="n">
+        <v>225989.3112821822</v>
+      </c>
+      <c r="U501" t="n">
+        <v>12.49999999966764</v>
+      </c>
+      <c r="V501" t="n">
+        <v>230.3456000015516</v>
+      </c>
+      <c r="W501" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y501" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z501" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA501" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>8</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>มรกต_G7/50</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G502" t="n">
+        <v>152.2965</v>
+      </c>
+      <c r="H502" t="n">
+        <v>152.2965</v>
+      </c>
+      <c r="I502" t="n">
+        <v>149479</v>
+      </c>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="n">
+        <v>4.912790322580645</v>
+      </c>
+      <c r="M502" t="n">
+        <v>4821.903225806452</v>
+      </c>
+      <c r="N502" t="inlineStr"/>
+      <c r="O502" t="n">
+        <v>981.4999031494485</v>
+      </c>
+      <c r="P502" t="n">
+        <v>34431829.94</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>1721591.49</v>
+      </c>
+      <c r="R502" t="n">
+        <v>230.3455999839442</v>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T502" t="n">
+        <v>226084.1840751429</v>
+      </c>
+      <c r="U502" t="n">
+        <v>4.999999979669974</v>
+      </c>
+      <c r="V502" t="n">
+        <v>230.3455999839442</v>
+      </c>
+      <c r="W502" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y502" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z502" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA502" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>8</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>มะลิวัลย์</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G503" t="n">
+        <v>758.1827</v>
+      </c>
+      <c r="H503" t="n">
+        <v>758.1827</v>
+      </c>
+      <c r="I503" t="n">
+        <v>807247</v>
+      </c>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="n">
+        <v>24.4575064516129</v>
+      </c>
+      <c r="M503" t="n">
+        <v>26040.22580645161</v>
+      </c>
+      <c r="N503" t="inlineStr"/>
+      <c r="O503" t="n">
+        <v>1064.713030249833</v>
+      </c>
+      <c r="P503" t="n">
+        <v>178551815.66</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>18568980.72</v>
+      </c>
+      <c r="R503" t="n">
+        <v>221.1860999917002</v>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T503" t="n">
+        <v>235499.7227713056</v>
+      </c>
+      <c r="U503" t="n">
+        <v>10.39977143405767</v>
+      </c>
+      <c r="V503" t="n">
+        <v>221.1860999917002</v>
+      </c>
+      <c r="W503" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y503" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z503" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA503" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>8</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>ยะลา_10A</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G504" t="n">
+        <v>35.5701</v>
+      </c>
+      <c r="H504" t="n">
+        <v>35.5701</v>
+      </c>
+      <c r="I504" t="n">
+        <v>26707</v>
+      </c>
+      <c r="J504" t="inlineStr"/>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="n">
+        <v>1.147422580645161</v>
+      </c>
+      <c r="M504" t="n">
+        <v>861.516129032258</v>
+      </c>
+      <c r="N504" t="inlineStr"/>
+      <c r="O504" t="n">
+        <v>750.8272397322471</v>
+      </c>
+      <c r="P504" t="n">
+        <v>5279995.27</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>659999.41</v>
+      </c>
+      <c r="R504" t="n">
+        <v>197.7008001647508</v>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T504" t="n">
+        <v>148439.1460805564</v>
+      </c>
+      <c r="U504" t="n">
+        <v>12.50000002367427</v>
+      </c>
+      <c r="V504" t="n">
+        <v>197.7008001647508</v>
+      </c>
+      <c r="W504" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y504" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z504" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA504" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>8</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>ยุงทอง</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G505" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="inlineStr"/>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="n">
+        <v>4.516129032258064e-05</v>
+      </c>
+      <c r="M505" t="n">
+        <v>0</v>
+      </c>
+      <c r="N505" t="inlineStr"/>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
+      <c r="P505" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>0</v>
+      </c>
+      <c r="R505" t="n">
+        <v>0</v>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T505" t="n">
+        <v>0</v>
+      </c>
+      <c r="U505" t="n">
+        <v>0</v>
+      </c>
+      <c r="V505" t="n">
+        <v>0</v>
+      </c>
+      <c r="W505" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y505" t="inlineStr">
+        <is>
+          <t>PTTEP Siam</t>
+        </is>
+      </c>
+      <c r="Z505" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="AA505" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>8</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>ลันตา</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G506" t="n">
+        <v>89.86239999999999</v>
+      </c>
+      <c r="H506" t="n">
+        <v>89.86239999999999</v>
+      </c>
+      <c r="I506" t="n">
+        <v>95667</v>
+      </c>
+      <c r="J506" t="inlineStr"/>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="n">
+        <v>2.898787096774194</v>
+      </c>
+      <c r="M506" t="n">
+        <v>3086.032258064516</v>
+      </c>
+      <c r="N506" t="inlineStr"/>
+      <c r="O506" t="n">
+        <v>1064.594313083114</v>
+      </c>
+      <c r="P506" t="n">
+        <v>21160210.63</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>1346164.08</v>
+      </c>
+      <c r="R506" t="n">
+        <v>221.1861000135888</v>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T506" t="n">
+        <v>235473.4642074995</v>
+      </c>
+      <c r="U506" t="n">
+        <v>6.361770700389291</v>
+      </c>
+      <c r="V506" t="n">
+        <v>221.1861000135888</v>
+      </c>
+      <c r="W506" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y506" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z506" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA506" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>8</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>สินภูฮ่อม_E5N</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G507" t="n">
+        <v>643.746</v>
+      </c>
+      <c r="H507" t="n">
+        <v>643.746</v>
+      </c>
+      <c r="I507" t="n">
+        <v>656801</v>
+      </c>
+      <c r="J507" t="inlineStr"/>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="n">
+        <v>20.766</v>
+      </c>
+      <c r="M507" t="n">
+        <v>21187.12903225806</v>
+      </c>
+      <c r="N507" t="inlineStr"/>
+      <c r="O507" t="n">
+        <v>1020.279737660506</v>
+      </c>
+      <c r="P507" t="n">
+        <v>187486383.38</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>23435797.92</v>
+      </c>
+      <c r="R507" t="n">
+        <v>285.4538640775517</v>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T507" t="n">
+        <v>291242.7935552221</v>
+      </c>
+      <c r="U507" t="n">
+        <v>12.49999999866657</v>
+      </c>
+      <c r="V507" t="n">
+        <v>285.4538640775517</v>
+      </c>
+      <c r="W507" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y507" t="inlineStr">
+        <is>
+          <t>PTTEP SP</t>
+        </is>
+      </c>
+      <c r="Z507" t="inlineStr">
+        <is>
+          <t>โคราช</t>
+        </is>
+      </c>
+      <c r="AA507" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>8</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>สินภูฮ่อม_EU1</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G508" t="n">
+        <v>2574.985</v>
+      </c>
+      <c r="H508" t="n">
+        <v>2574.985</v>
+      </c>
+      <c r="I508" t="n">
+        <v>2627208</v>
+      </c>
+      <c r="J508" t="inlineStr"/>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="n">
+        <v>83.06403225806451</v>
+      </c>
+      <c r="M508" t="n">
+        <v>84748.64516129032</v>
+      </c>
+      <c r="N508" t="inlineStr"/>
+      <c r="O508" t="n">
+        <v>1020.280894840164</v>
+      </c>
+      <c r="P508" t="n">
+        <v>749946007.74</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>93743250.97</v>
+      </c>
+      <c r="R508" t="n">
+        <v>285.4536099692145</v>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T508" t="n">
+        <v>291242.8646147453</v>
+      </c>
+      <c r="U508" t="n">
+        <v>12.50000000033336</v>
+      </c>
+      <c r="V508" t="n">
+        <v>285.4536099692145</v>
+      </c>
+      <c r="W508" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y508" t="inlineStr">
+        <is>
+          <t>PTTEP SP</t>
+        </is>
+      </c>
+      <c r="Z508" t="inlineStr">
+        <is>
+          <t>โคราช</t>
+        </is>
+      </c>
+      <c r="AA508" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>8</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>สิริกิติ์_NGV</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G509" t="n">
+        <v>77.676</v>
+      </c>
+      <c r="H509" t="n">
+        <v>77.676</v>
+      </c>
+      <c r="I509" t="n">
+        <v>82841</v>
+      </c>
+      <c r="J509" t="inlineStr"/>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="n">
+        <v>2.505677419354839</v>
+      </c>
+      <c r="M509" t="n">
+        <v>2672.290322580645</v>
+      </c>
+      <c r="N509" t="inlineStr"/>
+      <c r="O509" t="n">
+        <v>1066.494155208816</v>
+      </c>
+      <c r="P509" t="n">
+        <v>19113713.4</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>2389214.17</v>
+      </c>
+      <c r="R509" t="n">
+        <v>230.7277000519067</v>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T509" t="n">
+        <v>246069.7435501313</v>
+      </c>
+      <c r="U509" t="n">
+        <v>12.49999997384077</v>
+      </c>
+      <c r="V509" t="n">
+        <v>230.7277000519067</v>
+      </c>
+      <c r="W509" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y509" t="inlineStr">
+        <is>
+          <t>PTTEP Siam</t>
+        </is>
+      </c>
+      <c r="Z509" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="AA509" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB509" t="inlineStr">
+        <is>
+          <t>NGV</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>8</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>สิริกิติ์_กลุ่มแม่บ้าน</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G510" t="n">
+        <v>2.578</v>
+      </c>
+      <c r="H510" t="n">
+        <v>2.578</v>
+      </c>
+      <c r="I510" t="n">
+        <v>3820.562</v>
+      </c>
+      <c r="J510" t="inlineStr"/>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="n">
+        <v>0.08316129032258064</v>
+      </c>
+      <c r="M510" t="n">
+        <v>123.243935483871</v>
+      </c>
+      <c r="N510" t="inlineStr"/>
+      <c r="O510" t="n">
+        <v>1481.986811481769</v>
+      </c>
+      <c r="P510" t="n">
+        <v>759260.29</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>94907.53999999999</v>
+      </c>
+      <c r="R510" t="n">
+        <v>198.7300009789136</v>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T510" t="n">
+        <v>294515.240496509</v>
+      </c>
+      <c r="U510" t="n">
+        <v>12.50000049390177</v>
+      </c>
+      <c r="V510" t="n">
+        <v>198.7300009789136</v>
+      </c>
+      <c r="W510" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y510" t="inlineStr">
+        <is>
+          <t>PTTEP Siam</t>
+        </is>
+      </c>
+      <c r="Z510" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="AA510" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB510" t="inlineStr">
+        <is>
+          <t>ก๊าซหุงต้มชุมชน</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>8</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>สิริกิติ์_ประดู่เฒ่า_A</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G511" t="n">
+        <v>6.561</v>
+      </c>
+      <c r="H511" t="n">
+        <v>6.561</v>
+      </c>
+      <c r="I511" t="n">
+        <v>9532.314</v>
+      </c>
+      <c r="J511" t="inlineStr"/>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="n">
+        <v>0.2116451612903226</v>
+      </c>
+      <c r="M511" t="n">
+        <v>307.494</v>
+      </c>
+      <c r="N511" t="inlineStr"/>
+      <c r="O511" t="n">
+        <v>1452.875171467764</v>
+      </c>
+      <c r="P511" t="n">
+        <v>541816.73</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>67727.09</v>
+      </c>
+      <c r="R511" t="n">
+        <v>56.84000023499016</v>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T511" t="n">
+        <v>82581.42508763907</v>
+      </c>
+      <c r="U511" t="n">
+        <v>12.49999976929468</v>
+      </c>
+      <c r="V511" t="n">
+        <v>56.84000023499016</v>
+      </c>
+      <c r="W511" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y511" t="inlineStr">
+        <is>
+          <t>PTTEP Siam</t>
+        </is>
+      </c>
+      <c r="Z511" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="AA511" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>8</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G512" t="n">
+        <v>6.0266</v>
+      </c>
+      <c r="H512" t="n">
+        <v>6.0266</v>
+      </c>
+      <c r="I512" t="n">
+        <v>6409</v>
+      </c>
+      <c r="J512" t="inlineStr"/>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="n">
+        <v>0.1944064516129032</v>
+      </c>
+      <c r="M512" t="n">
+        <v>206.741935483871</v>
+      </c>
+      <c r="N512" t="inlineStr"/>
+      <c r="O512" t="n">
+        <v>1063.452029336608</v>
+      </c>
+      <c r="P512" t="n">
+        <v>1417581.72</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>90183.3</v>
+      </c>
+      <c r="R512" t="n">
+        <v>221.186100795756</v>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T512" t="n">
+        <v>235220.8077522981</v>
+      </c>
+      <c r="U512" t="n">
+        <v>6.361770805001633</v>
+      </c>
+      <c r="V512" t="n">
+        <v>221.186100795756</v>
+      </c>
+      <c r="W512" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y512" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z512" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA512" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>8</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>อาทิตย์</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G513" t="n">
+        <v>11040.835</v>
+      </c>
+      <c r="H513" t="n">
+        <v>11040.835</v>
+      </c>
+      <c r="I513" t="n">
+        <v>10756306</v>
+      </c>
+      <c r="J513" t="inlineStr"/>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="n">
+        <v>356.1559677419355</v>
+      </c>
+      <c r="M513" t="n">
+        <v>346977.6129032258</v>
+      </c>
+      <c r="N513" t="inlineStr"/>
+      <c r="O513" t="n">
+        <v>974.2293947876226</v>
+      </c>
+      <c r="P513" t="n">
+        <v>2754361899.26</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>344295237.41</v>
+      </c>
+      <c r="R513" t="n">
+        <v>256.0694999993493</v>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T513" t="n">
+        <v>249470.4340079351</v>
+      </c>
+      <c r="U513" t="n">
+        <v>12.50000000009077</v>
+      </c>
+      <c r="V513" t="n">
+        <v>256.0694999993493</v>
+      </c>
+      <c r="W513" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y513" t="inlineStr">
+        <is>
+          <t>PTTEP</t>
+        </is>
+      </c>
+      <c r="Z513" t="inlineStr">
+        <is>
+          <t>มาเลย์</t>
+        </is>
+      </c>
+      <c r="AA513" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>8</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>เบญจมาศ</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G514" t="n">
+        <v>1433.1558</v>
+      </c>
+      <c r="H514" t="n">
+        <v>1433.1558</v>
+      </c>
+      <c r="I514" t="n">
+        <v>1525939</v>
+      </c>
+      <c r="J514" t="inlineStr"/>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="n">
+        <v>46.23083225806452</v>
+      </c>
+      <c r="M514" t="n">
+        <v>49223.83870967742</v>
+      </c>
+      <c r="N514" t="inlineStr"/>
+      <c r="O514" t="n">
+        <v>1064.740483902727</v>
+      </c>
+      <c r="P514" t="n">
+        <v>337516496.24</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>35100944.15</v>
+      </c>
+      <c r="R514" t="n">
+        <v>221.1860999948229</v>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T514" t="n">
+        <v>235505.7951410447</v>
+      </c>
+      <c r="U514" t="n">
+        <v>10.39977143073936</v>
+      </c>
+      <c r="V514" t="n">
+        <v>221.1860999948229</v>
+      </c>
+      <c r="W514" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y514" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z514" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA514" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>8</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>ไพลิน</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G515" t="n">
+        <v>2260.3644</v>
+      </c>
+      <c r="H515" t="n">
+        <v>2260.3644</v>
+      </c>
+      <c r="I515" t="n">
+        <v>2216886</v>
+      </c>
+      <c r="J515" t="inlineStr"/>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="n">
+        <v>72.91498064516129</v>
+      </c>
+      <c r="M515" t="n">
+        <v>71512.45161290323</v>
+      </c>
+      <c r="N515" t="inlineStr"/>
+      <c r="O515" t="n">
+        <v>980.7648713632192</v>
+      </c>
+      <c r="P515" t="n">
+        <v>510649935.8</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>63831241.98</v>
+      </c>
+      <c r="R515" t="n">
+        <v>230.3455999992783</v>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T515" t="n">
+        <v>225914.8727523757</v>
+      </c>
+      <c r="U515" t="n">
+        <v>12.50000000097914</v>
+      </c>
+      <c r="V515" t="n">
+        <v>230.3455999992783</v>
+      </c>
+      <c r="W515" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y515" t="inlineStr">
+        <is>
+          <t>Chevron Offshore</t>
+        </is>
+      </c>
+      <c r="Z515" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA515" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>8</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติ</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>ไพลินเหนือ</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>ล้าน ลบ.ฟุต &amp; ล้านบีทียู</t>
+        </is>
+      </c>
+      <c r="G516" t="n">
+        <v>4684.2388</v>
+      </c>
+      <c r="H516" t="n">
+        <v>4684.2388</v>
+      </c>
+      <c r="I516" t="n">
+        <v>4617441</v>
+      </c>
+      <c r="J516" t="inlineStr"/>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="n">
+        <v>151.1044774193549</v>
+      </c>
+      <c r="M516" t="n">
+        <v>148949.7096774194</v>
+      </c>
+      <c r="N516" t="inlineStr"/>
+      <c r="O516" t="n">
+        <v>985.7398815790518</v>
+      </c>
+      <c r="P516" t="n">
+        <v>1063607217.61</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>132950902.2</v>
+      </c>
+      <c r="R516" t="n">
+        <v>230.3456000000866</v>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>บาท/MMBTU</t>
+        </is>
+      </c>
+      <c r="T516" t="n">
+        <v>227060.844466341</v>
+      </c>
+      <c r="U516" t="n">
+        <v>12.49999999988248</v>
+      </c>
+      <c r="V516" t="n">
+        <v>230.3456000000866</v>
+      </c>
+      <c r="W516" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y516" t="inlineStr">
+        <is>
+          <t>Chevron Offshore</t>
+        </is>
+      </c>
+      <c r="Z516" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA516" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>8</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติเหลว</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>G1/61</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G517" t="n">
+        <v>594418</v>
+      </c>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr"/>
+      <c r="J517" t="n">
+        <v>594418</v>
+      </c>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr"/>
+      <c r="N517" t="n">
+        <v>19174.77419354839</v>
+      </c>
+      <c r="O517" t="inlineStr"/>
+      <c r="P517" t="n">
+        <v>1553025269.55</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>577725400.36</v>
+      </c>
+      <c r="R517" t="n">
+        <v>2612.682101736488</v>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr"/>
+      <c r="U517" t="n">
+        <v>37.20000000562773</v>
+      </c>
+      <c r="V517" t="n">
+        <v>2612.682101736488</v>
+      </c>
+      <c r="W517" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y517" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="Z517" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA517" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="AB517" t="inlineStr">
+        <is>
+          <t>เอราวัณเดิม</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>8</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติเหลว</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>G2/61</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G518" t="n">
+        <v>760537</v>
+      </c>
+      <c r="H518" t="inlineStr"/>
+      <c r="I518" t="inlineStr"/>
+      <c r="J518" t="n">
+        <v>760537</v>
+      </c>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr"/>
+      <c r="N518" t="n">
+        <v>24533.45161290323</v>
+      </c>
+      <c r="O518" t="inlineStr"/>
+      <c r="P518" t="n">
+        <v>2001173563.23</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>760445954.04</v>
+      </c>
+      <c r="R518" t="n">
+        <v>2631.263913826678</v>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr"/>
+      <c r="U518" t="n">
+        <v>38.00000000062963</v>
+      </c>
+      <c r="V518" t="n">
+        <v>2631.263913826678</v>
+      </c>
+      <c r="W518" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y518" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="Z518" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA518" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="AB518" t="inlineStr">
+        <is>
+          <t>บงกชเดิม</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>8</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติเหลว</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>ตราด_11A</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G519" t="n">
+        <v>159</v>
+      </c>
+      <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr"/>
+      <c r="J519" t="n">
+        <v>159</v>
+      </c>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr"/>
+      <c r="N519" t="n">
+        <v>5.129032258064516</v>
+      </c>
+      <c r="O519" t="inlineStr"/>
+      <c r="P519" t="n">
+        <v>443070.72</v>
+      </c>
+      <c r="Q519" t="n">
+        <v>55383.84</v>
+      </c>
+      <c r="R519" t="n">
+        <v>2786.608301886792</v>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T519" t="inlineStr"/>
+      <c r="U519" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V519" t="n">
+        <v>2786.608301886792</v>
+      </c>
+      <c r="W519" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y519" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z519" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA519" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>8</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติเหลว</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>มรกต</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G520" t="n">
+        <v>171803</v>
+      </c>
+      <c r="H520" t="inlineStr"/>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="n">
+        <v>171803</v>
+      </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
+      <c r="N520" t="n">
+        <v>5542.032258064516</v>
+      </c>
+      <c r="O520" t="inlineStr"/>
+      <c r="P520" t="n">
+        <v>478688335.4</v>
+      </c>
+      <c r="Q520" t="n">
+        <v>59836041.92</v>
+      </c>
+      <c r="R520" t="n">
+        <v>2786.26296048381</v>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T520" t="inlineStr"/>
+      <c r="U520" t="n">
+        <v>12.49999999895548</v>
+      </c>
+      <c r="V520" t="n">
+        <v>2786.26296048381</v>
+      </c>
+      <c r="W520" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y520" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z520" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA520" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>8</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติเหลว</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>มรกต_G7/50</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G521" t="n">
+        <v>9157</v>
+      </c>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="n">
+        <v>9157</v>
+      </c>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr"/>
+      <c r="N521" t="n">
+        <v>295.3870967741935</v>
+      </c>
+      <c r="O521" t="inlineStr"/>
+      <c r="P521" t="n">
+        <v>25507397.77</v>
+      </c>
+      <c r="Q521" t="n">
+        <v>1275369.88</v>
+      </c>
+      <c r="R521" t="n">
+        <v>2785.562713770886</v>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T521" t="inlineStr"/>
+      <c r="U521" t="n">
+        <v>4.999999966676334</v>
+      </c>
+      <c r="V521" t="n">
+        <v>2785.562713770886</v>
+      </c>
+      <c r="W521" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y521" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z521" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA521" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>8</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติเหลว</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>สินภูฮ่อม_E5N</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G522" t="n">
+        <v>1265.44</v>
+      </c>
+      <c r="H522" t="inlineStr"/>
+      <c r="I522" t="inlineStr"/>
+      <c r="J522" t="n">
+        <v>1265.44</v>
+      </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr"/>
+      <c r="N522" t="n">
+        <v>40.82064516129032</v>
+      </c>
+      <c r="O522" t="inlineStr"/>
+      <c r="P522" t="n">
+        <v>3410867.7</v>
+      </c>
+      <c r="Q522" t="n">
+        <v>426358.45</v>
+      </c>
+      <c r="R522" t="n">
+        <v>2695.400572133013</v>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T522" t="inlineStr"/>
+      <c r="U522" t="n">
+        <v>12.49999963352434</v>
+      </c>
+      <c r="V522" t="n">
+        <v>2695.400572133013</v>
+      </c>
+      <c r="W522" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y522" t="inlineStr">
+        <is>
+          <t>PTTEP SP</t>
+        </is>
+      </c>
+      <c r="Z522" t="inlineStr">
+        <is>
+          <t>โคราช</t>
+        </is>
+      </c>
+      <c r="AA522" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>8</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติเหลว</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>สินภูฮ่อม_EU1</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G523" t="n">
+        <v>5061.59</v>
+      </c>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="n">
+        <v>5061.59</v>
+      </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
+      <c r="N523" t="n">
+        <v>163.2770967741936</v>
+      </c>
+      <c r="O523" t="inlineStr"/>
+      <c r="P523" t="n">
+        <v>13643012.45</v>
+      </c>
+      <c r="Q523" t="n">
+        <v>1705376.57</v>
+      </c>
+      <c r="R523" t="n">
+        <v>2695.400546073467</v>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T523" t="inlineStr"/>
+      <c r="U523" t="n">
+        <v>12.5000001007842</v>
+      </c>
+      <c r="V523" t="n">
+        <v>2695.400546073467</v>
+      </c>
+      <c r="W523" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y523" t="inlineStr">
+        <is>
+          <t>PTTEP SP</t>
+        </is>
+      </c>
+      <c r="Z523" t="inlineStr">
+        <is>
+          <t>โคราช</t>
+        </is>
+      </c>
+      <c r="AA523" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>8</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติเหลว</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>อาทิตย์</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G524" t="n">
+        <v>530156</v>
+      </c>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="n">
+        <v>530156</v>
+      </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
+      <c r="N524" t="n">
+        <v>17101.8064516129</v>
+      </c>
+      <c r="O524" t="inlineStr"/>
+      <c r="P524" t="n">
+        <v>1415553406.88</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>176944175.86</v>
+      </c>
+      <c r="R524" t="n">
+        <v>2670.069577407405</v>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T524" t="inlineStr"/>
+      <c r="U524" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V524" t="n">
+        <v>2670.069577407405</v>
+      </c>
+      <c r="W524" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y524" t="inlineStr">
+        <is>
+          <t>PTTEP</t>
+        </is>
+      </c>
+      <c r="Z524" t="inlineStr">
+        <is>
+          <t>มาเลย์</t>
+        </is>
+      </c>
+      <c r="AA524" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>8</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติเหลว</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>ไพลิน</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G525" t="n">
+        <v>91266</v>
+      </c>
+      <c r="H525" t="inlineStr"/>
+      <c r="I525" t="inlineStr"/>
+      <c r="J525" t="n">
+        <v>91266</v>
+      </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr"/>
+      <c r="N525" t="n">
+        <v>2944.064516129032</v>
+      </c>
+      <c r="O525" t="inlineStr"/>
+      <c r="P525" t="n">
+        <v>254339654.4</v>
+      </c>
+      <c r="Q525" t="n">
+        <v>31792456.81</v>
+      </c>
+      <c r="R525" t="n">
+        <v>2786.795240286635</v>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T525" t="inlineStr"/>
+      <c r="U525" t="n">
+        <v>12.50000000393175</v>
+      </c>
+      <c r="V525" t="n">
+        <v>2786.795240286635</v>
+      </c>
+      <c r="W525" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y525" t="inlineStr">
+        <is>
+          <t>Chevron Offshore</t>
+        </is>
+      </c>
+      <c r="Z525" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA525" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>8</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>ก๊าซธรรมชาติเหลว</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>ไพลินเหนือ</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G526" t="n">
+        <v>157353</v>
+      </c>
+      <c r="H526" t="inlineStr"/>
+      <c r="I526" t="inlineStr"/>
+      <c r="J526" t="n">
+        <v>157353</v>
+      </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr"/>
+      <c r="N526" t="n">
+        <v>5075.903225806452</v>
+      </c>
+      <c r="O526" t="inlineStr"/>
+      <c r="P526" t="n">
+        <v>438505768.66</v>
+      </c>
+      <c r="Q526" t="n">
+        <v>54813221.08</v>
+      </c>
+      <c r="R526" t="n">
+        <v>2786.764590824452</v>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T526" t="inlineStr"/>
+      <c r="U526" t="n">
+        <v>12.49999999942988</v>
+      </c>
+      <c r="V526" t="n">
+        <v>2786.764590824452</v>
+      </c>
+      <c r="W526" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y526" t="inlineStr">
+        <is>
+          <t>Chevron Offshore</t>
+        </is>
+      </c>
+      <c r="Z526" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA526" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>8</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>ก๊าซปิโตรเลียมเหลว (LPG)</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>สิริกิติ์ (LPG*, kgs.)</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>กิโลกรัม</t>
+        </is>
+      </c>
+      <c r="G527" t="n">
+        <v>4976630</v>
+      </c>
+      <c r="H527" t="inlineStr"/>
+      <c r="I527" t="inlineStr"/>
+      <c r="J527" t="inlineStr"/>
+      <c r="K527" t="n">
+        <v>4976630</v>
+      </c>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr"/>
+      <c r="N527" t="inlineStr"/>
+      <c r="O527" t="inlineStr"/>
+      <c r="P527" t="n">
+        <v>86951933.03</v>
+      </c>
+      <c r="Q527" t="n">
+        <v>10868991.62</v>
+      </c>
+      <c r="R527" t="n">
+        <v>17.47205097224427</v>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>บาท/กก.</t>
+        </is>
+      </c>
+      <c r="T527" t="inlineStr"/>
+      <c r="U527" t="n">
+        <v>12.49999998993697</v>
+      </c>
+      <c r="V527" t="n">
+        <v>17.47205097224427</v>
+      </c>
+      <c r="W527" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y527" t="inlineStr">
+        <is>
+          <t>PTTEP Siam</t>
+        </is>
+      </c>
+      <c r="Z527" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="AA527" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB527" t="inlineStr">
+        <is>
+          <t>LPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>8</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>1) บัวหลวง ส่งออกน้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G528" t="n">
+        <v>299488</v>
+      </c>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr"/>
+      <c r="J528" t="n">
+        <v>299488</v>
+      </c>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr"/>
+      <c r="N528" t="n">
+        <v>9660.903225806451</v>
+      </c>
+      <c r="O528" t="inlineStr"/>
+      <c r="P528" t="n">
+        <v>878997190.15</v>
+      </c>
+      <c r="Q528" t="n">
+        <v>70022216.7</v>
+      </c>
+      <c r="R528" t="n">
+        <v>2934.99969998798</v>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T528" t="inlineStr"/>
+      <c r="U528" t="n">
+        <v>7.966147956405957</v>
+      </c>
+      <c r="V528" t="n">
+        <v>2934.99969998798</v>
+      </c>
+      <c r="W528" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y528" t="inlineStr">
+        <is>
+          <t>Medco</t>
+        </is>
+      </c>
+      <c r="Z528" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="AA528" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB528" t="inlineStr">
+        <is>
+          <t>ส่งออกน้ำมันดิบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>8</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>G1/61</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G529" t="n">
+        <v>365074</v>
+      </c>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
+      <c r="J529" t="n">
+        <v>365074</v>
+      </c>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr"/>
+      <c r="N529" t="n">
+        <v>11776.58064516129</v>
+      </c>
+      <c r="O529" t="inlineStr"/>
+      <c r="P529" t="n">
+        <v>1078222442.36</v>
+      </c>
+      <c r="Q529" t="n">
+        <v>401098748.56</v>
+      </c>
+      <c r="R529" t="n">
+        <v>2953.435309991947</v>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T529" t="inlineStr"/>
+      <c r="U529" t="n">
+        <v>37.20000000019292</v>
+      </c>
+      <c r="V529" t="n">
+        <v>2953.435309991947</v>
+      </c>
+      <c r="W529" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y529" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="Z529" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA529" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+      <c r="AB529" t="inlineStr">
+        <is>
+          <t>เอราวัณเดิม</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>8</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>L1/64 บึงหญ้า</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G530" t="n">
+        <v>16114.435</v>
+      </c>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="inlineStr"/>
+      <c r="J530" t="n">
+        <v>16114.435</v>
+      </c>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr"/>
+      <c r="N530" t="n">
+        <v>519.8204838709677</v>
+      </c>
+      <c r="O530" t="inlineStr"/>
+      <c r="P530" t="n">
+        <v>59850645.59</v>
+      </c>
+      <c r="Q530" t="n">
+        <v>2992532.28</v>
+      </c>
+      <c r="R530" t="n">
+        <v>3714.101399769834</v>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T530" t="inlineStr"/>
+      <c r="U530" t="n">
+        <v>5.000000000835413</v>
+      </c>
+      <c r="V530" t="n">
+        <v>3714.101399769834</v>
+      </c>
+      <c r="W530" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y530" t="inlineStr">
+        <is>
+          <t>CNPCHK</t>
+        </is>
+      </c>
+      <c r="Z530" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="AA530" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>8</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>L33</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G531" t="n">
+        <v>214.336</v>
+      </c>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr"/>
+      <c r="J531" t="n">
+        <v>214.336</v>
+      </c>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr"/>
+      <c r="N531" t="n">
+        <v>6.914064516129033</v>
+      </c>
+      <c r="O531" t="inlineStr"/>
+      <c r="P531" t="n">
+        <v>765321.6899999999</v>
+      </c>
+      <c r="Q531" t="n">
+        <v>38266.08</v>
+      </c>
+      <c r="R531" t="n">
+        <v>3570.66330434458</v>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T531" t="inlineStr"/>
+      <c r="U531" t="n">
+        <v>4.999999412011961</v>
+      </c>
+      <c r="V531" t="n">
+        <v>3570.66330434458</v>
+      </c>
+      <c r="W531" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y531" t="inlineStr">
+        <is>
+          <t>Eco Orient</t>
+        </is>
+      </c>
+      <c r="Z531" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="AA531" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>8</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>L53A</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G532" t="n">
+        <v>796.162</v>
+      </c>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr"/>
+      <c r="J532" t="n">
+        <v>796.162</v>
+      </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr"/>
+      <c r="N532" t="n">
+        <v>25.68264516129032</v>
+      </c>
+      <c r="O532" t="inlineStr"/>
+      <c r="P532" t="n">
+        <v>2897578.81</v>
+      </c>
+      <c r="Q532" t="n">
+        <v>147715.39</v>
+      </c>
+      <c r="R532" t="n">
+        <v>3639.433695654904</v>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T532" t="inlineStr"/>
+      <c r="U532" t="n">
+        <v>5.097890331410865</v>
+      </c>
+      <c r="V532" t="n">
+        <v>3639.433695654904</v>
+      </c>
+      <c r="W532" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y532" t="inlineStr">
+        <is>
+          <t>Pan Orient</t>
+        </is>
+      </c>
+      <c r="Z532" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA532" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>8</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>L53D</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G533" t="n">
+        <v>4406.403</v>
+      </c>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="n">
+        <v>4406.403</v>
+      </c>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr"/>
+      <c r="N533" t="n">
+        <v>142.1420322580645</v>
+      </c>
+      <c r="O533" t="inlineStr"/>
+      <c r="P533" t="n">
+        <v>16105008.17</v>
+      </c>
+      <c r="Q533" t="n">
+        <v>821015.67</v>
+      </c>
+      <c r="R533" t="n">
+        <v>3654.910404245821</v>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T533" t="inlineStr"/>
+      <c r="U533" t="n">
+        <v>5.097890428452978</v>
+      </c>
+      <c r="V533" t="n">
+        <v>3654.910404245821</v>
+      </c>
+      <c r="W533" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y533" t="inlineStr">
+        <is>
+          <t>Pan Orient</t>
+        </is>
+      </c>
+      <c r="Z533" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA533" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>8</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>L53G</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G534" t="n">
+        <v>1953.316</v>
+      </c>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="inlineStr"/>
+      <c r="J534" t="n">
+        <v>1953.316</v>
+      </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr"/>
+      <c r="N534" t="n">
+        <v>63.0101935483871</v>
+      </c>
+      <c r="O534" t="inlineStr"/>
+      <c r="P534" t="n">
+        <v>7139194.96</v>
+      </c>
+      <c r="Q534" t="n">
+        <v>363948.33</v>
+      </c>
+      <c r="R534" t="n">
+        <v>3654.910398522308</v>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T534" t="inlineStr"/>
+      <c r="U534" t="n">
+        <v>5.097890336923927</v>
+      </c>
+      <c r="V534" t="n">
+        <v>3654.910398522308</v>
+      </c>
+      <c r="W534" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y534" t="inlineStr">
+        <is>
+          <t>Pan Orient</t>
+        </is>
+      </c>
+      <c r="Z534" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA534" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>8</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>กำแพงแสน</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G535" t="n">
+        <v>376.805</v>
+      </c>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr"/>
+      <c r="J535" t="n">
+        <v>376.805</v>
+      </c>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr"/>
+      <c r="N535" t="n">
+        <v>12.155</v>
+      </c>
+      <c r="O535" t="inlineStr"/>
+      <c r="P535" t="n">
+        <v>1391964.28</v>
+      </c>
+      <c r="Q535" t="n">
+        <v>69598.21000000001</v>
+      </c>
+      <c r="R535" t="n">
+        <v>3694.123697933945</v>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T535" t="inlineStr"/>
+      <c r="U535" t="n">
+        <v>4.999999712636304</v>
+      </c>
+      <c r="V535" t="n">
+        <v>3694.123697933945</v>
+      </c>
+      <c r="W535" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y535" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z535" t="inlineStr">
+        <is>
+          <t>กำแพงแสน</t>
+        </is>
+      </c>
+      <c r="AA535" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>8</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>จัสมิน</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G536" t="n">
+        <v>5659</v>
+      </c>
+      <c r="H536" t="inlineStr"/>
+      <c r="I536" t="inlineStr"/>
+      <c r="J536" t="n">
+        <v>5659</v>
+      </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr"/>
+      <c r="N536" t="n">
+        <v>182.5483870967742</v>
+      </c>
+      <c r="O536" t="inlineStr"/>
+      <c r="P536" t="n">
+        <v>16763078.96</v>
+      </c>
+      <c r="Q536" t="n">
+        <v>2095384.87</v>
+      </c>
+      <c r="R536" t="n">
+        <v>2962.198084467221</v>
+      </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T536" t="inlineStr"/>
+      <c r="U536" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V536" t="n">
+        <v>2962.198084467221</v>
+      </c>
+      <c r="W536" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y536" t="inlineStr">
+        <is>
+          <t>Valeura</t>
+        </is>
+      </c>
+      <c r="Z536" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA536" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>8</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>ดีดี</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G537" t="n">
+        <v>57942.09</v>
+      </c>
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="inlineStr"/>
+      <c r="J537" t="n">
+        <v>57942.09</v>
+      </c>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr"/>
+      <c r="N537" t="n">
+        <v>1869.099677419355</v>
+      </c>
+      <c r="O537" t="inlineStr"/>
+      <c r="P537" t="n">
+        <v>210635674.38</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>10737975.83</v>
+      </c>
+      <c r="R537" t="n">
+        <v>3635.279196521907</v>
+      </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T537" t="inlineStr"/>
+      <c r="U537" t="n">
+        <v>5.097890403231514</v>
+      </c>
+      <c r="V537" t="n">
+        <v>3635.279196521907</v>
+      </c>
+      <c r="W537" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y537" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z537" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA537" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>8</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>นงเยาว์</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G538" t="n">
+        <v>276458</v>
+      </c>
+      <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr"/>
+      <c r="J538" t="n">
+        <v>276458</v>
+      </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr"/>
+      <c r="N538" t="n">
+        <v>8918</v>
+      </c>
+      <c r="O538" t="inlineStr"/>
+      <c r="P538" t="n">
+        <v>865172269.96</v>
+      </c>
+      <c r="Q538" t="n">
+        <v>66566734.63</v>
+      </c>
+      <c r="R538" t="n">
+        <v>3129.488999992766</v>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T538" t="inlineStr"/>
+      <c r="U538" t="n">
+        <v>7.694043942610136</v>
+      </c>
+      <c r="V538" t="n">
+        <v>3129.488999992766</v>
+      </c>
+      <c r="W538" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y538" t="inlineStr">
+        <is>
+          <t>Valeura</t>
+        </is>
+      </c>
+      <c r="Z538" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA538" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>8</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>นาสนุนตะวันออก</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G539" t="n">
+        <v>2716.002</v>
+      </c>
+      <c r="H539" t="inlineStr"/>
+      <c r="I539" t="inlineStr"/>
+      <c r="J539" t="n">
+        <v>2716.002</v>
+      </c>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr"/>
+      <c r="N539" t="n">
+        <v>87.61296774193548</v>
+      </c>
+      <c r="O539" t="inlineStr"/>
+      <c r="P539" t="n">
+        <v>9751113.140000001</v>
+      </c>
+      <c r="Q539" t="n">
+        <v>487555.65</v>
+      </c>
+      <c r="R539" t="n">
+        <v>3590.245198641238</v>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T539" t="inlineStr"/>
+      <c r="U539" t="n">
+        <v>4.999999928213324</v>
+      </c>
+      <c r="V539" t="n">
+        <v>3590.245198641238</v>
+      </c>
+      <c r="W539" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y539" t="inlineStr">
+        <is>
+          <t>Eco Orient</t>
+        </is>
+      </c>
+      <c r="Z539" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="AA539" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>8</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>บัวหลวง</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G540" t="n">
+        <v>306031.16</v>
+      </c>
+      <c r="H540" t="inlineStr"/>
+      <c r="I540" t="inlineStr"/>
+      <c r="J540" t="n">
+        <v>306031.16</v>
+      </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr"/>
+      <c r="N540" t="n">
+        <v>9871.972903225806</v>
+      </c>
+      <c r="O540" t="inlineStr"/>
+      <c r="P540" t="n">
+        <v>898201362.79</v>
+      </c>
+      <c r="Q540" t="n">
+        <v>71552049.51000001</v>
+      </c>
+      <c r="R540" t="n">
+        <v>2934.99969999787</v>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T540" t="inlineStr"/>
+      <c r="U540" t="n">
+        <v>7.96614795681722</v>
+      </c>
+      <c r="V540" t="n">
+        <v>2934.99969999787</v>
+      </c>
+      <c r="W540" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y540" t="inlineStr">
+        <is>
+          <t>Medco</t>
+        </is>
+      </c>
+      <c r="Z540" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="AA540" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>8</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>บึงหญ้าหนองสา</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G541" t="n">
+        <v>9743.574000000001</v>
+      </c>
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="inlineStr"/>
+      <c r="J541" t="n">
+        <v>9743.574000000001</v>
+      </c>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr"/>
+      <c r="N541" t="n">
+        <v>314.3088387096774</v>
+      </c>
+      <c r="O541" t="inlineStr"/>
+      <c r="P541" t="n">
+        <v>36188621.83</v>
+      </c>
+      <c r="Q541" t="n">
+        <v>1809431.09</v>
+      </c>
+      <c r="R541" t="n">
+        <v>3714.10139954805</v>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T541" t="inlineStr"/>
+      <c r="U541" t="n">
+        <v>4.999999995855052</v>
+      </c>
+      <c r="V541" t="n">
+        <v>3714.10139954805</v>
+      </c>
+      <c r="W541" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y541" t="inlineStr">
+        <is>
+          <t>CNPCHK</t>
+        </is>
+      </c>
+      <c r="Z541" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="AA541" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>8</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>บูรพา</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G542" t="n">
+        <v>6099.154</v>
+      </c>
+      <c r="H542" t="inlineStr"/>
+      <c r="I542" t="inlineStr"/>
+      <c r="J542" t="n">
+        <v>6099.154</v>
+      </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr"/>
+      <c r="N542" t="n">
+        <v>196.7469032258065</v>
+      </c>
+      <c r="O542" t="inlineStr"/>
+      <c r="P542" t="n">
+        <v>23778460.65</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>1188923.02</v>
+      </c>
+      <c r="R542" t="n">
+        <v>3898.649001156553</v>
+      </c>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T542" t="inlineStr"/>
+      <c r="U542" t="n">
+        <v>4.999999947431417</v>
+      </c>
+      <c r="V542" t="n">
+        <v>3898.649001156553</v>
+      </c>
+      <c r="W542" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y542" t="inlineStr">
+        <is>
+          <t>UAC Utilities</t>
+        </is>
+      </c>
+      <c r="Z542" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="AA542" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>8</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>บ่อรังเหนือ</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G543" t="n">
+        <v>1077.661</v>
+      </c>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr"/>
+      <c r="J543" t="n">
+        <v>1077.661</v>
+      </c>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr"/>
+      <c r="N543" t="n">
+        <v>34.76325806451613</v>
+      </c>
+      <c r="O543" t="inlineStr"/>
+      <c r="P543" t="n">
+        <v>3685639.63</v>
+      </c>
+      <c r="Q543" t="n">
+        <v>184281.99</v>
+      </c>
+      <c r="R543" t="n">
+        <v>3420.036198767516</v>
+      </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T543" t="inlineStr"/>
+      <c r="U543" t="n">
+        <v>5.000000230624827</v>
+      </c>
+      <c r="V543" t="n">
+        <v>3420.036198767516</v>
+      </c>
+      <c r="W543" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y543" t="inlineStr">
+        <is>
+          <t>Eco Orient</t>
+        </is>
+      </c>
+      <c r="Z543" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="AA543" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>8</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>มะลิวัลย์</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G544" t="n">
+        <v>24278</v>
+      </c>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
+      <c r="J544" t="n">
+        <v>24278</v>
+      </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr"/>
+      <c r="N544" t="n">
+        <v>783.1612903225806</v>
+      </c>
+      <c r="O544" t="inlineStr"/>
+      <c r="P544" t="n">
+        <v>74912967.19</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>7790777.36</v>
+      </c>
+      <c r="R544" t="n">
+        <v>3085.63173202076</v>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T544" t="inlineStr"/>
+      <c r="U544" t="n">
+        <v>10.39977143108006</v>
+      </c>
+      <c r="V544" t="n">
+        <v>3085.63173202076</v>
+      </c>
+      <c r="W544" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y544" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z544" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA544" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>8</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>รสสุคนธ์</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G545" t="n">
+        <v>260798</v>
+      </c>
+      <c r="H545" t="inlineStr"/>
+      <c r="I545" t="inlineStr"/>
+      <c r="J545" t="n">
+        <v>260798</v>
+      </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr"/>
+      <c r="N545" t="n">
+        <v>8412.838709677419</v>
+      </c>
+      <c r="O545" t="inlineStr"/>
+      <c r="P545" t="n">
+        <v>843084041.78</v>
+      </c>
+      <c r="Q545" t="n">
+        <v>63699884.31</v>
+      </c>
+      <c r="R545" t="n">
+        <v>3232.708999992331</v>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T545" t="inlineStr"/>
+      <c r="U545" t="n">
+        <v>7.555579414777047</v>
+      </c>
+      <c r="V545" t="n">
+        <v>3232.708999992331</v>
+      </c>
+      <c r="W545" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y545" t="inlineStr">
+        <is>
+          <t>Valeura</t>
+        </is>
+      </c>
+      <c r="Z545" t="inlineStr">
+        <is>
+          <t>มาเลย์</t>
+        </is>
+      </c>
+      <c r="AA545" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>8</v>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>ลันตา</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G546" t="n">
+        <v>121157</v>
+      </c>
+      <c r="H546" t="inlineStr"/>
+      <c r="I546" t="inlineStr"/>
+      <c r="J546" t="n">
+        <v>121157</v>
+      </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr"/>
+      <c r="N546" t="n">
+        <v>3908.290322580645</v>
+      </c>
+      <c r="O546" t="inlineStr"/>
+      <c r="P546" t="n">
+        <v>376272728.13</v>
+      </c>
+      <c r="Q546" t="n">
+        <v>23937608.13</v>
+      </c>
+      <c r="R546" t="n">
+        <v>3105.662307006611</v>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T546" t="inlineStr"/>
+      <c r="U546" t="n">
+        <v>6.361770689298986</v>
+      </c>
+      <c r="V546" t="n">
+        <v>3105.662307006611</v>
+      </c>
+      <c r="W546" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y546" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z546" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA546" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>8</v>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>วังไผ่สูง</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G547" t="n">
+        <v>1830.137</v>
+      </c>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr"/>
+      <c r="J547" t="n">
+        <v>1830.137</v>
+      </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr"/>
+      <c r="N547" t="n">
+        <v>59.03667741935484</v>
+      </c>
+      <c r="O547" t="inlineStr"/>
+      <c r="P547" t="n">
+        <v>4946361.06</v>
+      </c>
+      <c r="Q547" t="n">
+        <v>247318.05</v>
+      </c>
+      <c r="R547" t="n">
+        <v>2702.72720566821</v>
+      </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T547" t="inlineStr"/>
+      <c r="U547" t="n">
+        <v>4.999999939349353</v>
+      </c>
+      <c r="V547" t="n">
+        <v>2702.72720566821</v>
+      </c>
+      <c r="W547" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y547" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z547" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="AA547" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>8</v>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>วิเชียรบุรีส่วนขยาย-3</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G548" t="n">
+        <v>1116.572</v>
+      </c>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr"/>
+      <c r="J548" t="n">
+        <v>1116.572</v>
+      </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr"/>
+      <c r="N548" t="n">
+        <v>36.01845161290322</v>
+      </c>
+      <c r="O548" t="inlineStr"/>
+      <c r="P548" t="n">
+        <v>4038393.94</v>
+      </c>
+      <c r="Q548" t="n">
+        <v>201919.7</v>
+      </c>
+      <c r="R548" t="n">
+        <v>3616.778801546161</v>
+      </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T548" t="inlineStr"/>
+      <c r="U548" t="n">
+        <v>5.000000074286958</v>
+      </c>
+      <c r="V548" t="n">
+        <v>3616.778801546161</v>
+      </c>
+      <c r="W548" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y548" t="inlineStr">
+        <is>
+          <t>Eco Orient</t>
+        </is>
+      </c>
+      <c r="Z548" t="inlineStr">
+        <is>
+          <t>เพชรบูรณ์</t>
+        </is>
+      </c>
+      <c r="AA548" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>8</v>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>สังขจาย</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G549" t="n">
+        <v>1382.226</v>
+      </c>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr"/>
+      <c r="J549" t="n">
+        <v>1382.226</v>
+      </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr"/>
+      <c r="N549" t="n">
+        <v>44.58793548387097</v>
+      </c>
+      <c r="O549" t="inlineStr"/>
+      <c r="P549" t="n">
+        <v>5112951.14</v>
+      </c>
+      <c r="Q549" t="n">
+        <v>255647.55</v>
+      </c>
+      <c r="R549" t="n">
+        <v>3699.070296753208</v>
+      </c>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T549" t="inlineStr"/>
+      <c r="U549" t="n">
+        <v>4.999999863092765</v>
+      </c>
+      <c r="V549" t="n">
+        <v>3699.070296753208</v>
+      </c>
+      <c r="W549" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y549" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z549" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA549" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>8</v>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>สิริกิติ์</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G550" t="n">
+        <v>735357.817</v>
+      </c>
+      <c r="H550" t="inlineStr"/>
+      <c r="I550" t="inlineStr"/>
+      <c r="J550" t="n">
+        <v>735357.817</v>
+      </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr"/>
+      <c r="N550" t="n">
+        <v>23721.21990322581</v>
+      </c>
+      <c r="O550" t="inlineStr"/>
+      <c r="P550" t="n">
+        <v>2025614269.69</v>
+      </c>
+      <c r="Q550" t="n">
+        <v>253201783.72</v>
+      </c>
+      <c r="R550" t="n">
+        <v>2754.596772974809</v>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T550" t="inlineStr"/>
+      <c r="U550" t="n">
+        <v>12.50000000043197</v>
+      </c>
+      <c r="V550" t="n">
+        <v>2754.596772974809</v>
+      </c>
+      <c r="W550" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y550" t="inlineStr">
+        <is>
+          <t>PTTEP Siam</t>
+        </is>
+      </c>
+      <c r="Z550" t="inlineStr">
+        <is>
+          <t>พิษณุโลก</t>
+        </is>
+      </c>
+      <c r="AA550" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>8</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G551" t="n">
+        <v>43858</v>
+      </c>
+      <c r="H551" t="inlineStr"/>
+      <c r="I551" t="inlineStr"/>
+      <c r="J551" t="n">
+        <v>43858</v>
+      </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr"/>
+      <c r="N551" t="n">
+        <v>1414.774193548387</v>
+      </c>
+      <c r="O551" t="inlineStr"/>
+      <c r="P551" t="n">
+        <v>135522495.64</v>
+      </c>
+      <c r="Q551" t="n">
+        <v>8621630.4</v>
+      </c>
+      <c r="R551" t="n">
+        <v>3090.029085685621</v>
+      </c>
+      <c r="S551" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T551" t="inlineStr"/>
+      <c r="U551" t="n">
+        <v>6.361770685585938</v>
+      </c>
+      <c r="V551" t="n">
+        <v>3090.029085685621</v>
+      </c>
+      <c r="W551" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y551" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z551" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA551" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>8</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>หนองผักชี จี</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G552" t="n">
+        <v>8363.236999999999</v>
+      </c>
+      <c r="H552" t="inlineStr"/>
+      <c r="I552" t="inlineStr"/>
+      <c r="J552" t="n">
+        <v>8363.236999999999</v>
+      </c>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr"/>
+      <c r="N552" t="n">
+        <v>269.7818387096774</v>
+      </c>
+      <c r="O552" t="inlineStr"/>
+      <c r="P552" t="n">
+        <v>30894832.01</v>
+      </c>
+      <c r="Q552" t="n">
+        <v>1544741.6</v>
+      </c>
+      <c r="R552" t="n">
+        <v>3694.123699950152</v>
+      </c>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T552" t="inlineStr"/>
+      <c r="U552" t="n">
+        <v>4.999999998381607</v>
+      </c>
+      <c r="V552" t="n">
+        <v>3694.123699950152</v>
+      </c>
+      <c r="W552" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y552" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z552" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA552" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>8</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>หนองผักชี_ซี</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G553" t="n">
+        <v>6237.113</v>
+      </c>
+      <c r="H553" t="inlineStr"/>
+      <c r="I553" t="inlineStr"/>
+      <c r="J553" t="n">
+        <v>6237.113</v>
+      </c>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr"/>
+      <c r="N553" t="n">
+        <v>201.1971935483871</v>
+      </c>
+      <c r="O553" t="inlineStr"/>
+      <c r="P553" t="n">
+        <v>23040666.95</v>
+      </c>
+      <c r="Q553" t="n">
+        <v>1152033.35</v>
+      </c>
+      <c r="R553" t="n">
+        <v>3694.123699538552</v>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T553" t="inlineStr"/>
+      <c r="U553" t="n">
+        <v>5.00000001085038</v>
+      </c>
+      <c r="V553" t="n">
+        <v>3694.123699538552</v>
+      </c>
+      <c r="W553" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y553" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z553" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA553" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>8</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>หนองผักชี_ดี</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G554" t="n">
+        <v>1366.659</v>
+      </c>
+      <c r="H554" t="inlineStr"/>
+      <c r="I554" t="inlineStr"/>
+      <c r="J554" t="n">
+        <v>1366.659</v>
+      </c>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr"/>
+      <c r="N554" t="n">
+        <v>44.08577419354839</v>
+      </c>
+      <c r="O554" t="inlineStr"/>
+      <c r="P554" t="n">
+        <v>5048607.4</v>
+      </c>
+      <c r="Q554" t="n">
+        <v>252430.37</v>
+      </c>
+      <c r="R554" t="n">
+        <v>3694.1236987427</v>
+      </c>
+      <c r="S554" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T554" t="inlineStr"/>
+      <c r="U554" t="n">
+        <v>5</v>
+      </c>
+      <c r="V554" t="n">
+        <v>3694.1236987427</v>
+      </c>
+      <c r="W554" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y554" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z554" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA554" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>8</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>หนองผักชี_บี</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G555" t="n">
+        <v>2081.895</v>
+      </c>
+      <c r="H555" t="inlineStr"/>
+      <c r="I555" t="inlineStr"/>
+      <c r="J555" t="n">
+        <v>2081.895</v>
+      </c>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr"/>
+      <c r="M555" t="inlineStr"/>
+      <c r="N555" t="n">
+        <v>67.15790322580645</v>
+      </c>
+      <c r="O555" t="inlineStr"/>
+      <c r="P555" t="n">
+        <v>7690777.66</v>
+      </c>
+      <c r="Q555" t="n">
+        <v>384538.88</v>
+      </c>
+      <c r="R555" t="n">
+        <v>3694.123699802344</v>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T555" t="inlineStr"/>
+      <c r="U555" t="n">
+        <v>4.999999960992241</v>
+      </c>
+      <c r="V555" t="n">
+        <v>3694.123699802344</v>
+      </c>
+      <c r="W555" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y555" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z555" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA555" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>8</v>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>หนองผักชี_เอ</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G556" t="n">
+        <v>1391.096</v>
+      </c>
+      <c r="H556" t="inlineStr"/>
+      <c r="I556" t="inlineStr"/>
+      <c r="J556" t="n">
+        <v>1391.096</v>
+      </c>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr"/>
+      <c r="M556" t="inlineStr"/>
+      <c r="N556" t="n">
+        <v>44.87406451612903</v>
+      </c>
+      <c r="O556" t="inlineStr"/>
+      <c r="P556" t="n">
+        <v>5138880.7</v>
+      </c>
+      <c r="Q556" t="n">
+        <v>256944.04</v>
+      </c>
+      <c r="R556" t="n">
+        <v>3694.123698148798</v>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr"/>
+      <c r="U556" t="n">
+        <v>5.000000097297452</v>
+      </c>
+      <c r="V556" t="n">
+        <v>3694.123698148798</v>
+      </c>
+      <c r="W556" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y556" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z556" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA556" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>8</v>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>อรุโณทัย</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G557" t="n">
+        <v>1264.762</v>
+      </c>
+      <c r="H557" t="inlineStr"/>
+      <c r="I557" t="inlineStr"/>
+      <c r="J557" t="n">
+        <v>1264.762</v>
+      </c>
+      <c r="K557" t="inlineStr"/>
+      <c r="L557" t="inlineStr"/>
+      <c r="M557" t="inlineStr"/>
+      <c r="N557" t="n">
+        <v>40.79877419354838</v>
+      </c>
+      <c r="O557" t="inlineStr"/>
+      <c r="P557" t="n">
+        <v>4930863.11</v>
+      </c>
+      <c r="Q557" t="n">
+        <v>246543.16</v>
+      </c>
+      <c r="R557" t="n">
+        <v>3898.649002737274</v>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr"/>
+      <c r="U557" t="n">
+        <v>5.000000091261913</v>
+      </c>
+      <c r="V557" t="n">
+        <v>3898.649002737274</v>
+      </c>
+      <c r="W557" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X557" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y557" t="inlineStr">
+        <is>
+          <t>UAC Utilities</t>
+        </is>
+      </c>
+      <c r="Z557" t="inlineStr">
+        <is>
+          <t>สุโขทัย</t>
+        </is>
+      </c>
+      <c r="AA557" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>8</v>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>อู่ทอง</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G558" t="n">
+        <v>2526.211</v>
+      </c>
+      <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr"/>
+      <c r="J558" t="n">
+        <v>2526.211</v>
+      </c>
+      <c r="K558" t="inlineStr"/>
+      <c r="L558" t="inlineStr"/>
+      <c r="M558" t="inlineStr"/>
+      <c r="N558" t="n">
+        <v>81.49067741935484</v>
+      </c>
+      <c r="O558" t="inlineStr"/>
+      <c r="P558" t="n">
+        <v>9332135.93</v>
+      </c>
+      <c r="Q558" t="n">
+        <v>466606.8</v>
+      </c>
+      <c r="R558" t="n">
+        <v>3694.123701464367</v>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T558" t="inlineStr"/>
+      <c r="U558" t="n">
+        <v>5.000000037504812</v>
+      </c>
+      <c r="V558" t="n">
+        <v>3694.123701464367</v>
+      </c>
+      <c r="W558" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="Y558" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="Z558" t="inlineStr">
+        <is>
+          <t>สุพรรณบุรี</t>
+        </is>
+      </c>
+      <c r="AA558" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>สิงหาคม</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>8</v>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>น้ำมันดิบ</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>เบญจมาศ</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>บาร์เรล</t>
+        </is>
+      </c>
+      <c r="G559" t="n">
+        <v>369785</v>
+      </c>
+      <c r="H559" t="inlineStr"/>
+      <c r="I559" t="inlineStr"/>
+      <c r="J559" t="n">
+        <v>369785</v>
+      </c>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr"/>
+      <c r="M559" t="inlineStr"/>
+      <c r="N559" t="n">
+        <v>11928.54838709677</v>
+      </c>
+      <c r="O559" t="inlineStr"/>
+      <c r="P559" t="n">
+        <v>1146776336.44</v>
+      </c>
+      <c r="Q559" t="n">
+        <v>119262117.82</v>
+      </c>
+      <c r="R559" t="n">
+        <v>3101.197551117541</v>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>บาท/บาร์เรล</t>
+        </is>
+      </c>
+      <c r="T559" t="inlineStr"/>
+      <c r="U559" t="n">
+        <v>10.39977143147476</v>
+      </c>
+      <c r="V559" t="n">
+        <v>3101.197551117541</v>
+      </c>
+      <c r="W559" t="inlineStr">
+        <is>
+          <t>DMF_salevalue_2026_08.xlsx</t>
+        </is>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="Y559" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="Z559" t="inlineStr">
+        <is>
+          <t>ปัตตานี</t>
+        </is>
+      </c>
+      <c r="AA559" t="inlineStr">
+        <is>
+          <t>สัมปทาน</t>
+        </is>
+      </c>
+      <c r="AB559" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/petroleum_sale_flat_table.xlsx
+++ b/output/petroleum_sale_flat_table.xlsx
@@ -610,13 +610,13 @@
         <v>933.5047022544491</v>
       </c>
       <c r="P2" t="n">
-        <v>2925175703.57</v>
+        <v>2924529422.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>1088165361.74</v>
+        <v>1087924945.14</v>
       </c>
       <c r="R2" t="n">
-        <v>141.6689999999516</v>
+        <v>141.6377000002761</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>132248.6776636404</v>
+        <v>132219.4589667627</v>
       </c>
       <c r="U2" t="n">
-        <v>37.20000000040886</v>
+        <v>37.199999999483</v>
       </c>
       <c r="V2" t="n">
-        <v>141.6689999999516</v>
+        <v>141.6377000002761</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -714,13 +714,13 @@
         <v>977.8256455132412</v>
       </c>
       <c r="P3" t="n">
-        <v>46634951.23</v>
+        <v>46626392.31</v>
       </c>
       <c r="Q3" t="n">
-        <v>2331747.52</v>
+        <v>2331319.63</v>
       </c>
       <c r="R3" t="n">
-        <v>267.5311000137681</v>
+        <v>267.4819999885266</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>261598.7705658303</v>
+        <v>261550.7593019538</v>
       </c>
       <c r="U3" t="n">
-        <v>4.999999911010951</v>
+        <v>5.000000031098266</v>
       </c>
       <c r="V3" t="n">
-        <v>267.5311000137681</v>
+        <v>267.4819999885266</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -818,13 +818,13 @@
         <v>966.6674552081721</v>
       </c>
       <c r="P4" t="n">
-        <v>2906095155.98</v>
+        <v>2905453090.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>1104316159.27</v>
+        <v>1104072174.38</v>
       </c>
       <c r="R4" t="n">
-        <v>141.6690000002438</v>
+        <v>141.6377000001219</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>136946.8117121221</v>
+        <v>136916.5550206563</v>
       </c>
       <c r="U4" t="n">
-        <v>37.99999999991741</v>
+        <v>38.00000000004819</v>
       </c>
       <c r="V4" t="n">
-        <v>141.6690000002438</v>
+        <v>141.6377000001219</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -922,13 +922,13 @@
         <v>802.1726503651254</v>
       </c>
       <c r="P5" t="n">
-        <v>20935416.2</v>
+        <v>20931202.39</v>
       </c>
       <c r="Q5" t="n">
-        <v>2051686.03</v>
+        <v>2051273.07</v>
       </c>
       <c r="R5" t="n">
-        <v>217.6110001145566</v>
+        <v>217.5672001060145</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>174561.5927104995</v>
+        <v>174526.4575415613</v>
       </c>
       <c r="U5" t="n">
-        <v>9.800072806768465</v>
+        <v>9.800072789798293</v>
       </c>
       <c r="V5" t="n">
-        <v>217.6110001145566</v>
+        <v>217.5672001060145</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1622,13 +1622,13 @@
         <v>1043.068357227369</v>
       </c>
       <c r="P12" t="n">
-        <v>274641319.73</v>
+        <v>274586044.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>26915049.18</v>
+        <v>26909632.14</v>
       </c>
       <c r="R12" t="n">
-        <v>214.9070465212363</v>
+        <v>214.8637932507743</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>224162.7399714917</v>
+        <v>224117.6238537262</v>
       </c>
       <c r="U12" t="n">
-        <v>9.800072766348558</v>
+        <v>9.800072772846375</v>
       </c>
       <c r="V12" t="n">
-        <v>214.9070465212363</v>
+        <v>214.8637932507743</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1822,13 +1822,13 @@
         <v>1043.127271737207</v>
       </c>
       <c r="P14" t="n">
-        <v>26231283.63</v>
+        <v>26226004.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1842150.67</v>
+        <v>1841779.88</v>
       </c>
       <c r="R14" t="n">
-        <v>213.9582677814029</v>
+        <v>213.9152063621534</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>223185.7041364335</v>
+        <v>223140.7855956546</v>
       </c>
       <c r="U14" t="n">
-        <v>7.022724072462785</v>
+        <v>7.022723930537904</v>
       </c>
       <c r="V14" t="n">
-        <v>213.9582677814029</v>
+        <v>213.9152063621534</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2530,13 +2530,13 @@
         <v>1043.592976557392</v>
       </c>
       <c r="P21" t="n">
-        <v>1923564.25</v>
+        <v>1923177.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>135086.61</v>
+        <v>135059.42</v>
       </c>
       <c r="R21" t="n">
-        <v>215.1878565835105</v>
+        <v>215.14454636984</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2544,13 +2544,13 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>224568.5357709909</v>
+        <v>224523.3375361913</v>
       </c>
       <c r="U21" t="n">
-        <v>7.022724091487975</v>
+        <v>7.022724012260753</v>
       </c>
       <c r="V21" t="n">
-        <v>215.1878565835105</v>
+        <v>215.14454636984</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         <v>982.2684290017886</v>
       </c>
       <c r="P22" t="n">
-        <v>2743380614.83</v>
+        <v>2742334984.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>342922576.86</v>
+        <v>342791873.1</v>
       </c>
       <c r="R22" t="n">
-        <v>256.0695000000933</v>
+        <v>255.9718999988986</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="T22" t="n">
-        <v>251528.9854803652</v>
+        <v>251433.116080521</v>
       </c>
       <c r="U22" t="n">
-        <v>12.50000000022782</v>
+        <v>12.49999999986326</v>
       </c>
       <c r="V22" t="n">
-        <v>256.0695000000933</v>
+        <v>255.9718999988986</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2730,13 +2730,13 @@
         <v>1043.385732852776</v>
       </c>
       <c r="P23" t="n">
-        <v>207949652.49</v>
+        <v>207907799.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>20379217.26</v>
+        <v>20375115.66</v>
       </c>
       <c r="R23" t="n">
-        <v>214.8222457768944</v>
+        <v>214.7790096259535</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2744,13 +2744,13 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>224142.4663430042</v>
+        <v>224097.354359969</v>
       </c>
       <c r="U23" t="n">
-        <v>9.80007276568063</v>
+        <v>9.800072774614673</v>
       </c>
       <c r="V23" t="n">
-        <v>214.8222457768944</v>
+        <v>214.7790096259535</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3024,13 +3024,13 @@
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>962881704.38</v>
+        <v>943975140.21</v>
       </c>
       <c r="Q26" t="n">
-        <v>358191994.06</v>
+        <v>351158752.18</v>
       </c>
       <c r="R26" t="n">
-        <v>1885.400749514396</v>
+        <v>1848.380157997588</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -3039,10 +3039,10 @@
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
-        <v>37.20000000318212</v>
+        <v>37.20000000231786</v>
       </c>
       <c r="V26" t="n">
-        <v>1885.400749514396</v>
+        <v>1848.380157997588</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3120,13 +3120,13 @@
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>74769802.25</v>
+        <v>73918710.90000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>3738490.04</v>
+        <v>3695935.57</v>
       </c>
       <c r="R27" t="n">
-        <v>1867.9375</v>
+        <v>1846.675099930049</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
-        <v>4.999999903035721</v>
+        <v>5.000000033820935</v>
       </c>
       <c r="V27" t="n">
-        <v>1867.9375</v>
+        <v>1846.675099930049</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3216,13 +3216,13 @@
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1203609695.38</v>
+        <v>1186830964.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>457371684.26</v>
+        <v>450995766.38</v>
       </c>
       <c r="R28" t="n">
-        <v>1879.679750158903</v>
+        <v>1853.476370901118</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3231,10 +3231,10 @@
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>38.00000000129609</v>
+        <v>38.00000000025277</v>
       </c>
       <c r="V28" t="n">
-        <v>1879.679750158903</v>
+        <v>1853.476370901118</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3312,13 +3312,13 @@
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>409277130.61</v>
+        <v>399227471.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>51159641.32</v>
+        <v>49903433.93</v>
       </c>
       <c r="R29" t="n">
-        <v>1891.220469620025</v>
+        <v>1844.782201572023</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3327,10 +3327,10 @@
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
-        <v>12.49999999847292</v>
+        <v>12.49999999937379</v>
       </c>
       <c r="V29" t="n">
-        <v>1891.220469620025</v>
+        <v>1844.782201572023</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3404,13 +3404,13 @@
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>3552489.8</v>
+        <v>3465259.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>177624.49</v>
+        <v>173262.98</v>
       </c>
       <c r="R30" t="n">
-        <v>1890.627887174029</v>
+        <v>1844.204172432145</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3419,10 +3419,10 @@
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>4.999999942284267</v>
       </c>
       <c r="V30" t="n">
-        <v>1890.627887174029</v>
+        <v>1844.204172432145</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3680,13 +3680,13 @@
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>891722962.11</v>
+        <v>879923381.1900001</v>
       </c>
       <c r="Q33" t="n">
-        <v>111465370.26</v>
+        <v>109990422.65</v>
       </c>
       <c r="R33" t="n">
-        <v>1896.560590987688</v>
+        <v>1871.464657481512</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3695,10 +3695,10 @@
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="n">
-        <v>12.49999999957947</v>
+        <v>12.50000000014206</v>
       </c>
       <c r="V33" t="n">
-        <v>1896.560590987688</v>
+        <v>1871.464657481512</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3772,13 +3772,13 @@
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>206161299.73</v>
+        <v>201099079.83</v>
       </c>
       <c r="Q34" t="n">
-        <v>25770162.47</v>
+        <v>25137384.98</v>
       </c>
       <c r="R34" t="n">
-        <v>1891.006399900937</v>
+        <v>1844.573387297977</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="n">
-        <v>12.50000000181896</v>
+        <v>12.50000000062158</v>
       </c>
       <c r="V34" t="n">
-        <v>1891.006399900937</v>
+        <v>1844.573387297977</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3864,13 +3864,13 @@
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>403286490.97</v>
+        <v>393383929.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>50410811.37</v>
+        <v>49172991.21</v>
       </c>
       <c r="R35" t="n">
-        <v>1890.966807192761</v>
+        <v>1844.534766633844</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="n">
-        <v>12.49999999969005</v>
+        <v>12.5</v>
       </c>
       <c r="V35" t="n">
-        <v>1890.966807192761</v>
+        <v>1844.534766633844</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>124093090.33</v>
       </c>
       <c r="Q52" t="n">
-        <v>12161213.14</v>
+        <v>12161213.16</v>
       </c>
       <c r="R52" t="n">
         <v>1981.747905234917</v>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="n">
-        <v>9.800072758007525</v>
+        <v>9.800072774124457</v>
       </c>
       <c r="V52" t="n">
         <v>1981.747905234917</v>
@@ -5713,7 +5713,7 @@
         <v>274348239</v>
       </c>
       <c r="Q55" t="n">
-        <v>19266719.79</v>
+        <v>19266719.45</v>
       </c>
       <c r="R55" t="n">
         <v>1980.63920153052</v>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="n">
-        <v>7.022724060568875</v>
+        <v>7.022723936638791</v>
       </c>
       <c r="V55" t="n">
         <v>1980.63920153052</v>
@@ -6265,7 +6265,7 @@
         <v>123692588.86</v>
       </c>
       <c r="Q61" t="n">
-        <v>8686589.199999999</v>
+        <v>8686589.039999999</v>
       </c>
       <c r="R61" t="n">
         <v>1980.570811009879</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="n">
-        <v>7.022724061367826</v>
+        <v>7.022723932014887</v>
       </c>
       <c r="V61" t="n">
         <v>1980.570811009879</v>
@@ -7001,7 +7001,7 @@
         <v>429974786.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>42137841.95</v>
+        <v>42137841.98</v>
       </c>
       <c r="R69" t="n">
         <v>1980.829908139385</v>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="n">
-        <v>9.800072765429469</v>
+        <v>9.800072772406621</v>
       </c>
       <c r="V69" t="n">
         <v>1980.829908139385</v>

--- a/output/petroleum_sale_flat_table.xlsx
+++ b/output/petroleum_sale_flat_table.xlsx
@@ -610,13 +610,13 @@
         <v>933.5047022544491</v>
       </c>
       <c r="P2" t="n">
-        <v>2924529422.46</v>
+        <v>2925175703.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>1087924945.14</v>
+        <v>1088165361.74</v>
       </c>
       <c r="R2" t="n">
-        <v>141.6377000002761</v>
+        <v>141.6689999999516</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>132219.4589667627</v>
+        <v>132248.6776636404</v>
       </c>
       <c r="U2" t="n">
-        <v>37.199999999483</v>
+        <v>37.20000000040886</v>
       </c>
       <c r="V2" t="n">
-        <v>141.6377000002761</v>
+        <v>141.6689999999516</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -714,13 +714,13 @@
         <v>977.8256455132412</v>
       </c>
       <c r="P3" t="n">
-        <v>46626392.31</v>
+        <v>46634951.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>2331319.63</v>
+        <v>2331747.52</v>
       </c>
       <c r="R3" t="n">
-        <v>267.4819999885266</v>
+        <v>267.5311000137681</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>261550.7593019538</v>
+        <v>261598.7705658303</v>
       </c>
       <c r="U3" t="n">
-        <v>5.000000031098266</v>
+        <v>4.999999911010951</v>
       </c>
       <c r="V3" t="n">
-        <v>267.4819999885266</v>
+        <v>267.5311000137681</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -818,13 +818,13 @@
         <v>966.6674552081721</v>
       </c>
       <c r="P4" t="n">
-        <v>2905453090.47</v>
+        <v>2906095155.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1104072174.38</v>
+        <v>1104316159.27</v>
       </c>
       <c r="R4" t="n">
-        <v>141.6377000001219</v>
+        <v>141.6690000002438</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>136916.5550206563</v>
+        <v>136946.8117121221</v>
       </c>
       <c r="U4" t="n">
-        <v>38.00000000004819</v>
+        <v>37.99999999991741</v>
       </c>
       <c r="V4" t="n">
-        <v>141.6377000001219</v>
+        <v>141.6690000002438</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -922,13 +922,13 @@
         <v>802.1726503651254</v>
       </c>
       <c r="P5" t="n">
-        <v>20931202.39</v>
+        <v>20935416.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2051273.07</v>
+        <v>2051686.03</v>
       </c>
       <c r="R5" t="n">
-        <v>217.5672001060145</v>
+        <v>217.6110001145566</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>174526.4575415613</v>
+        <v>174561.5927104995</v>
       </c>
       <c r="U5" t="n">
-        <v>9.800072789798293</v>
+        <v>9.800072806768465</v>
       </c>
       <c r="V5" t="n">
-        <v>217.5672001060145</v>
+        <v>217.6110001145566</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1622,13 +1622,13 @@
         <v>1043.068357227369</v>
       </c>
       <c r="P12" t="n">
-        <v>274586044.04</v>
+        <v>274641319.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>26909632.14</v>
+        <v>26915049.18</v>
       </c>
       <c r="R12" t="n">
-        <v>214.8637932507743</v>
+        <v>214.9070465212363</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>224117.6238537262</v>
+        <v>224162.7399714917</v>
       </c>
       <c r="U12" t="n">
-        <v>9.800072772846375</v>
+        <v>9.800072766348558</v>
       </c>
       <c r="V12" t="n">
-        <v>214.8637932507743</v>
+        <v>214.9070465212363</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1822,13 +1822,13 @@
         <v>1043.127271737207</v>
       </c>
       <c r="P14" t="n">
-        <v>26226004.3</v>
+        <v>26231283.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>1841779.88</v>
+        <v>1842150.67</v>
       </c>
       <c r="R14" t="n">
-        <v>213.9152063621534</v>
+        <v>213.9582677814029</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>223140.7855956546</v>
+        <v>223185.7041364335</v>
       </c>
       <c r="U14" t="n">
-        <v>7.022723930537904</v>
+        <v>7.022724072462785</v>
       </c>
       <c r="V14" t="n">
-        <v>213.9152063621534</v>
+        <v>213.9582677814029</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2530,13 +2530,13 @@
         <v>1043.592976557392</v>
       </c>
       <c r="P21" t="n">
-        <v>1923177.1</v>
+        <v>1923564.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>135059.42</v>
+        <v>135086.61</v>
       </c>
       <c r="R21" t="n">
-        <v>215.14454636984</v>
+        <v>215.1878565835105</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2544,13 +2544,13 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>224523.3375361913</v>
+        <v>224568.5357709909</v>
       </c>
       <c r="U21" t="n">
-        <v>7.022724012260753</v>
+        <v>7.022724091487975</v>
       </c>
       <c r="V21" t="n">
-        <v>215.14454636984</v>
+        <v>215.1878565835105</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2630,13 +2630,13 @@
         <v>982.2684290017886</v>
       </c>
       <c r="P22" t="n">
-        <v>2742334984.83</v>
+        <v>2743380614.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>342791873.1</v>
+        <v>342922576.86</v>
       </c>
       <c r="R22" t="n">
-        <v>255.9718999988986</v>
+        <v>256.0695000000933</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="T22" t="n">
-        <v>251433.116080521</v>
+        <v>251528.9854803652</v>
       </c>
       <c r="U22" t="n">
-        <v>12.49999999986326</v>
+        <v>12.50000000022782</v>
       </c>
       <c r="V22" t="n">
-        <v>255.9718999988986</v>
+        <v>256.0695000000933</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2730,13 +2730,13 @@
         <v>1043.385732852776</v>
       </c>
       <c r="P23" t="n">
-        <v>207907799.55</v>
+        <v>207949652.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>20375115.66</v>
+        <v>20379217.26</v>
       </c>
       <c r="R23" t="n">
-        <v>214.7790096259535</v>
+        <v>214.8222457768944</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2744,13 +2744,13 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>224097.354359969</v>
+        <v>224142.4663430042</v>
       </c>
       <c r="U23" t="n">
-        <v>9.800072774614673</v>
+        <v>9.80007276568063</v>
       </c>
       <c r="V23" t="n">
-        <v>214.7790096259535</v>
+        <v>214.8222457768944</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3024,13 +3024,13 @@
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>943975140.21</v>
+        <v>962881704.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>351158752.18</v>
+        <v>358191994.06</v>
       </c>
       <c r="R26" t="n">
-        <v>1848.380157997588</v>
+        <v>1885.400749514396</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -3039,10 +3039,10 @@
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
-        <v>37.20000000231786</v>
+        <v>37.20000000318212</v>
       </c>
       <c r="V26" t="n">
-        <v>1848.380157997588</v>
+        <v>1885.400749514396</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3120,13 +3120,13 @@
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>73918710.90000001</v>
+        <v>74769802.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3695935.57</v>
+        <v>3738490.04</v>
       </c>
       <c r="R27" t="n">
-        <v>1846.675099930049</v>
+        <v>1867.9375</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
-        <v>5.000000033820935</v>
+        <v>4.999999903035721</v>
       </c>
       <c r="V27" t="n">
-        <v>1846.675099930049</v>
+        <v>1867.9375</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3216,13 +3216,13 @@
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1186830964.15</v>
+        <v>1203609695.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>450995766.38</v>
+        <v>457371684.26</v>
       </c>
       <c r="R28" t="n">
-        <v>1853.476370901118</v>
+        <v>1879.679750158903</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3231,10 +3231,10 @@
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>38.00000000025277</v>
+        <v>38.00000000129609</v>
       </c>
       <c r="V28" t="n">
-        <v>1853.476370901118</v>
+        <v>1879.679750158903</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3312,13 +3312,13 @@
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>399227471.46</v>
+        <v>409277130.61</v>
       </c>
       <c r="Q29" t="n">
-        <v>49903433.93</v>
+        <v>51159641.32</v>
       </c>
       <c r="R29" t="n">
-        <v>1844.782201572023</v>
+        <v>1891.220469620025</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3327,10 +3327,10 @@
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
-        <v>12.49999999937379</v>
+        <v>12.49999999847292</v>
       </c>
       <c r="V29" t="n">
-        <v>1844.782201572023</v>
+        <v>1891.220469620025</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3404,13 +3404,13 @@
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>3465259.64</v>
+        <v>3552489.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>173262.98</v>
+        <v>177624.49</v>
       </c>
       <c r="R30" t="n">
-        <v>1844.204172432145</v>
+        <v>1890.627887174029</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3419,10 +3419,10 @@
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
-        <v>4.999999942284267</v>
+        <v>5</v>
       </c>
       <c r="V30" t="n">
-        <v>1844.204172432145</v>
+        <v>1890.627887174029</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3680,13 +3680,13 @@
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>879923381.1900001</v>
+        <v>891722962.11</v>
       </c>
       <c r="Q33" t="n">
-        <v>109990422.65</v>
+        <v>111465370.26</v>
       </c>
       <c r="R33" t="n">
-        <v>1871.464657481512</v>
+        <v>1896.560590987688</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3695,10 +3695,10 @@
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="n">
-        <v>12.50000000014206</v>
+        <v>12.49999999957947</v>
       </c>
       <c r="V33" t="n">
-        <v>1871.464657481512</v>
+        <v>1896.560590987688</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3772,13 +3772,13 @@
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>201099079.83</v>
+        <v>206161299.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>25137384.98</v>
+        <v>25770162.47</v>
       </c>
       <c r="R34" t="n">
-        <v>1844.573387297977</v>
+        <v>1891.006399900937</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="n">
-        <v>12.50000000062158</v>
+        <v>12.50000000181896</v>
       </c>
       <c r="V34" t="n">
-        <v>1844.573387297977</v>
+        <v>1891.006399900937</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3864,13 +3864,13 @@
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>393383929.68</v>
+        <v>403286490.97</v>
       </c>
       <c r="Q35" t="n">
-        <v>49172991.21</v>
+        <v>50410811.37</v>
       </c>
       <c r="R35" t="n">
-        <v>1844.534766633844</v>
+        <v>1890.966807192761</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="n">
-        <v>12.5</v>
+        <v>12.49999999969005</v>
       </c>
       <c r="V35" t="n">
-        <v>1844.534766633844</v>
+        <v>1890.966807192761</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>124093090.33</v>
       </c>
       <c r="Q52" t="n">
-        <v>12161213.16</v>
+        <v>12161213.14</v>
       </c>
       <c r="R52" t="n">
         <v>1981.747905234917</v>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="n">
-        <v>9.800072774124457</v>
+        <v>9.800072758007525</v>
       </c>
       <c r="V52" t="n">
         <v>1981.747905234917</v>
@@ -5713,7 +5713,7 @@
         <v>274348239</v>
       </c>
       <c r="Q55" t="n">
-        <v>19266719.45</v>
+        <v>19266719.79</v>
       </c>
       <c r="R55" t="n">
         <v>1980.63920153052</v>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="n">
-        <v>7.022723936638791</v>
+        <v>7.022724060568875</v>
       </c>
       <c r="V55" t="n">
         <v>1980.63920153052</v>
@@ -6265,7 +6265,7 @@
         <v>123692588.86</v>
       </c>
       <c r="Q61" t="n">
-        <v>8686589.039999999</v>
+        <v>8686589.199999999</v>
       </c>
       <c r="R61" t="n">
         <v>1980.570811009879</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="n">
-        <v>7.022723932014887</v>
+        <v>7.022724061367826</v>
       </c>
       <c r="V61" t="n">
         <v>1980.570811009879</v>
@@ -7001,7 +7001,7 @@
         <v>429974786.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>42137841.98</v>
+        <v>42137841.95</v>
       </c>
       <c r="R69" t="n">
         <v>1980.829908139385</v>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="n">
-        <v>9.800072772406621</v>
+        <v>9.800072765429469</v>
       </c>
       <c r="V69" t="n">
         <v>1980.829908139385</v>
@@ -23346,13 +23346,13 @@
       </c>
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="n">
-        <v>1925905387.79</v>
+        <v>1805753059.8</v>
       </c>
       <c r="Q239" t="n">
-        <v>716436804.35</v>
+        <v>671740138.26</v>
       </c>
       <c r="R239" t="n">
-        <v>3301.904925480609</v>
+        <v>3095.907493772192</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -23361,10 +23361,10 @@
       </c>
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="n">
-        <v>37.20000000478321</v>
+        <v>37.20000000079745</v>
       </c>
       <c r="V239" t="n">
-        <v>3301.904925480609</v>
+        <v>3095.907493772192</v>
       </c>
       <c r="W239" t="inlineStr">
         <is>
@@ -23442,13 +23442,13 @@
       </c>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="n">
-        <v>2206681741.97</v>
+        <v>2066767947.58</v>
       </c>
       <c r="Q240" t="n">
-        <v>838539061.95</v>
+        <v>785371820.0599999</v>
       </c>
       <c r="R240" t="n">
-        <v>3292.282150586564</v>
+        <v>3083.536286092391</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -23457,10 +23457,10 @@
       </c>
       <c r="T240" t="inlineStr"/>
       <c r="U240" t="n">
-        <v>38.00000000006345</v>
+        <v>37.99999999901295</v>
       </c>
       <c r="V240" t="n">
-        <v>3292.282150586564</v>
+        <v>3083.536286092391</v>
       </c>
       <c r="W240" t="inlineStr">
         <is>
@@ -23538,13 +23538,13 @@
       </c>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="n">
-        <v>1093487.88</v>
+        <v>1043242.06</v>
       </c>
       <c r="Q241" t="n">
-        <v>136685.97</v>
+        <v>130405.24</v>
       </c>
       <c r="R241" t="n">
-        <v>3313.599636363636</v>
+        <v>3161.339575757576</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -23553,10 +23553,10 @@
       </c>
       <c r="T241" t="inlineStr"/>
       <c r="U241" t="n">
-        <v>12.49999862824269</v>
+        <v>12.49999832253696</v>
       </c>
       <c r="V241" t="n">
-        <v>3313.599636363636</v>
+        <v>3161.339575757576</v>
       </c>
       <c r="W241" t="inlineStr">
         <is>
@@ -23630,13 +23630,13 @@
       </c>
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="n">
-        <v>733269339.76</v>
+        <v>699575575.28</v>
       </c>
       <c r="Q242" t="n">
-        <v>91658667.48</v>
+        <v>87446946.91</v>
       </c>
       <c r="R242" t="n">
-        <v>3299.685631434948</v>
+        <v>3148.064904240766</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -23645,10 +23645,10 @@
       </c>
       <c r="T242" t="inlineStr"/>
       <c r="U242" t="n">
-        <v>12.50000000136376</v>
+        <v>12.5</v>
       </c>
       <c r="V242" t="n">
-        <v>3299.685631434948</v>
+        <v>3148.064904240766</v>
       </c>
       <c r="W242" t="inlineStr">
         <is>
@@ -23722,13 +23722,13 @@
       </c>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="n">
-        <v>3821126.03</v>
+        <v>3645545.09</v>
       </c>
       <c r="Q243" t="n">
-        <v>191056.3</v>
+        <v>182277.25</v>
       </c>
       <c r="R243" t="n">
-        <v>3299.76341105354</v>
+        <v>3148.139110535406</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -23737,10 +23737,10 @@
       </c>
       <c r="T243" t="inlineStr"/>
       <c r="U243" t="n">
-        <v>4.999999960744556</v>
+        <v>4.99999987656167</v>
       </c>
       <c r="V243" t="n">
-        <v>3299.76341105354</v>
+        <v>3148.139110535406</v>
       </c>
       <c r="W243" t="inlineStr">
         <is>
@@ -23998,13 +23998,13 @@
       </c>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="n">
-        <v>1857727025.98</v>
+        <v>1736308859.48</v>
       </c>
       <c r="Q246" t="n">
-        <v>232215878.25</v>
+        <v>217038607.43</v>
       </c>
       <c r="R246" t="n">
-        <v>3376.51906792199</v>
+        <v>3155.83500150857</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -24013,10 +24013,10 @@
       </c>
       <c r="T246" t="inlineStr"/>
       <c r="U246" t="n">
-        <v>12.50000000013457</v>
+        <v>12.49999999971203</v>
       </c>
       <c r="V246" t="n">
-        <v>3376.51906792199</v>
+        <v>3155.83500150857</v>
       </c>
       <c r="W246" t="inlineStr">
         <is>
@@ -24090,13 +24090,13 @@
       </c>
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="n">
-        <v>319304435.23</v>
+        <v>304632379.75</v>
       </c>
       <c r="Q247" t="n">
-        <v>39913054.4</v>
+        <v>38079047.47</v>
       </c>
       <c r="R247" t="n">
-        <v>3300.133690558628</v>
+        <v>3148.492375071056</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -24105,10 +24105,10 @@
       </c>
       <c r="T247" t="inlineStr"/>
       <c r="U247" t="n">
-        <v>12.49999999882557</v>
+        <v>12.50000000041033</v>
       </c>
       <c r="V247" t="n">
-        <v>3300.133690558628</v>
+        <v>3148.492375071056</v>
       </c>
       <c r="W247" t="inlineStr">
         <is>
@@ -24182,13 +24182,13 @@
       </c>
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="n">
-        <v>609133310.92</v>
+        <v>581143603.58</v>
       </c>
       <c r="Q248" t="n">
-        <v>76141663.86</v>
+        <v>72642950.45</v>
       </c>
       <c r="R248" t="n">
-        <v>3300.247659016535</v>
+        <v>3148.601107318553</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -24197,10 +24197,10 @@
       </c>
       <c r="T248" t="inlineStr"/>
       <c r="U248" t="n">
-        <v>12.49999999917916</v>
+        <v>12.50000000043019</v>
       </c>
       <c r="V248" t="n">
-        <v>3300.247659016535</v>
+        <v>3148.601107318553</v>
       </c>
       <c r="W248" t="inlineStr">
         <is>

--- a/output/petroleum_sale_flat_table.xlsx
+++ b/output/petroleum_sale_flat_table.xlsx
@@ -23346,13 +23346,13 @@
       </c>
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="n">
-        <v>1805753059.8</v>
+        <v>1925905387.79</v>
       </c>
       <c r="Q239" t="n">
-        <v>671740138.26</v>
+        <v>716436804.35</v>
       </c>
       <c r="R239" t="n">
-        <v>3095.907493772192</v>
+        <v>3301.904925480609</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -23361,10 +23361,10 @@
       </c>
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="n">
-        <v>37.20000000079745</v>
+        <v>37.20000000478321</v>
       </c>
       <c r="V239" t="n">
-        <v>3095.907493772192</v>
+        <v>3301.904925480609</v>
       </c>
       <c r="W239" t="inlineStr">
         <is>
@@ -23442,13 +23442,13 @@
       </c>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="n">
-        <v>2066767947.58</v>
+        <v>2206681741.97</v>
       </c>
       <c r="Q240" t="n">
-        <v>785371820.0599999</v>
+        <v>838539061.95</v>
       </c>
       <c r="R240" t="n">
-        <v>3083.536286092391</v>
+        <v>3292.282150586564</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -23457,10 +23457,10 @@
       </c>
       <c r="T240" t="inlineStr"/>
       <c r="U240" t="n">
-        <v>37.99999999901295</v>
+        <v>38.00000000006345</v>
       </c>
       <c r="V240" t="n">
-        <v>3083.536286092391</v>
+        <v>3292.282150586564</v>
       </c>
       <c r="W240" t="inlineStr">
         <is>
@@ -23538,13 +23538,13 @@
       </c>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="n">
-        <v>1043242.06</v>
+        <v>1093487.88</v>
       </c>
       <c r="Q241" t="n">
-        <v>130405.24</v>
+        <v>136685.97</v>
       </c>
       <c r="R241" t="n">
-        <v>3161.339575757576</v>
+        <v>3313.599636363636</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -23553,10 +23553,10 @@
       </c>
       <c r="T241" t="inlineStr"/>
       <c r="U241" t="n">
-        <v>12.49999832253696</v>
+        <v>12.49999862824269</v>
       </c>
       <c r="V241" t="n">
-        <v>3161.339575757576</v>
+        <v>3313.599636363636</v>
       </c>
       <c r="W241" t="inlineStr">
         <is>
@@ -23630,13 +23630,13 @@
       </c>
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="n">
-        <v>699575575.28</v>
+        <v>733269339.76</v>
       </c>
       <c r="Q242" t="n">
-        <v>87446946.91</v>
+        <v>91658667.48</v>
       </c>
       <c r="R242" t="n">
-        <v>3148.064904240766</v>
+        <v>3299.685631434948</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -23645,10 +23645,10 @@
       </c>
       <c r="T242" t="inlineStr"/>
       <c r="U242" t="n">
-        <v>12.5</v>
+        <v>12.50000000136376</v>
       </c>
       <c r="V242" t="n">
-        <v>3148.064904240766</v>
+        <v>3299.685631434948</v>
       </c>
       <c r="W242" t="inlineStr">
         <is>
@@ -23722,13 +23722,13 @@
       </c>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="n">
-        <v>3645545.09</v>
+        <v>3821126.03</v>
       </c>
       <c r="Q243" t="n">
-        <v>182277.25</v>
+        <v>191056.3</v>
       </c>
       <c r="R243" t="n">
-        <v>3148.139110535406</v>
+        <v>3299.76341105354</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -23737,10 +23737,10 @@
       </c>
       <c r="T243" t="inlineStr"/>
       <c r="U243" t="n">
-        <v>4.99999987656167</v>
+        <v>4.999999960744556</v>
       </c>
       <c r="V243" t="n">
-        <v>3148.139110535406</v>
+        <v>3299.76341105354</v>
       </c>
       <c r="W243" t="inlineStr">
         <is>
@@ -23998,13 +23998,13 @@
       </c>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="n">
-        <v>1736308859.48</v>
+        <v>1857727025.98</v>
       </c>
       <c r="Q246" t="n">
-        <v>217038607.43</v>
+        <v>232215878.25</v>
       </c>
       <c r="R246" t="n">
-        <v>3155.83500150857</v>
+        <v>3376.51906792199</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -24013,10 +24013,10 @@
       </c>
       <c r="T246" t="inlineStr"/>
       <c r="U246" t="n">
-        <v>12.49999999971203</v>
+        <v>12.50000000013457</v>
       </c>
       <c r="V246" t="n">
-        <v>3155.83500150857</v>
+        <v>3376.51906792199</v>
       </c>
       <c r="W246" t="inlineStr">
         <is>
@@ -24090,13 +24090,13 @@
       </c>
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="n">
-        <v>304632379.75</v>
+        <v>319304435.23</v>
       </c>
       <c r="Q247" t="n">
-        <v>38079047.47</v>
+        <v>39913054.4</v>
       </c>
       <c r="R247" t="n">
-        <v>3148.492375071056</v>
+        <v>3300.133690558628</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -24105,10 +24105,10 @@
       </c>
       <c r="T247" t="inlineStr"/>
       <c r="U247" t="n">
-        <v>12.50000000041033</v>
+        <v>12.49999999882557</v>
       </c>
       <c r="V247" t="n">
-        <v>3148.492375071056</v>
+        <v>3300.133690558628</v>
       </c>
       <c r="W247" t="inlineStr">
         <is>
@@ -24182,13 +24182,13 @@
       </c>
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="n">
-        <v>581143603.58</v>
+        <v>609133310.92</v>
       </c>
       <c r="Q248" t="n">
-        <v>72642950.45</v>
+        <v>76141663.86</v>
       </c>
       <c r="R248" t="n">
-        <v>3148.601107318553</v>
+        <v>3300.247659016535</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -24197,10 +24197,10 @@
       </c>
       <c r="T248" t="inlineStr"/>
       <c r="U248" t="n">
-        <v>12.50000000043019</v>
+        <v>12.49999999917916</v>
       </c>
       <c r="V248" t="n">
-        <v>3148.601107318553</v>
+        <v>3300.247659016535</v>
       </c>
       <c r="W248" t="inlineStr">
         <is>

--- a/output/petroleum_sale_flat_table.xlsx
+++ b/output/petroleum_sale_flat_table.xlsx
@@ -28329,7 +28329,7 @@
         <v>4825970.67</v>
       </c>
       <c r="Q292" t="n">
-        <v>241298.54</v>
+        <v>241298.53</v>
       </c>
       <c r="R292" t="n">
         <v>230.3456002100138</v>
@@ -28343,7 +28343,7 @@
         <v>225696.1580911582</v>
       </c>
       <c r="U292" t="n">
-        <v>5.00000013468793</v>
+        <v>4.999999927475731</v>
       </c>
       <c r="V292" t="n">
         <v>230.3456002100138</v>
@@ -29537,7 +29537,7 @@
         <v>2877790983.24</v>
       </c>
       <c r="Q304" t="n">
-        <v>359723872.91</v>
+        <v>359723872.9</v>
       </c>
       <c r="R304" t="n">
         <v>256.0695</v>
@@ -29551,7 +29551,7 @@
         <v>249689.7074852225</v>
       </c>
       <c r="U304" t="n">
-        <v>12.50000000017375</v>
+        <v>12.49999999982626</v>
       </c>
       <c r="V304" t="n">
         <v>256.0695</v>
@@ -29737,7 +29737,7 @@
         <v>620186409.3200001</v>
       </c>
       <c r="Q306" t="n">
-        <v>77523301.17</v>
+        <v>77523301.16</v>
       </c>
       <c r="R306" t="n">
         <v>230.3456000017828</v>
@@ -29751,7 +29751,7 @@
         <v>225494.0414093505</v>
       </c>
       <c r="U306" t="n">
-        <v>12.50000000080621</v>
+        <v>12.49999999919379</v>
       </c>
       <c r="V306" t="n">
         <v>230.3456000017828</v>
@@ -29928,13 +29928,13 @@
       </c>
       <c r="O308" t="inlineStr"/>
       <c r="P308" t="n">
-        <v>2043192757.57</v>
+        <v>1961197480.34</v>
       </c>
       <c r="Q308" t="n">
-        <v>760067706.17</v>
+        <v>729565462.55</v>
       </c>
       <c r="R308" t="n">
-        <v>3384.472909494182</v>
+        <v>3248.650778438154</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -29943,10 +29943,10 @@
       </c>
       <c r="T308" t="inlineStr"/>
       <c r="U308" t="n">
-        <v>37.20000001732387</v>
+        <v>37.19999999304098</v>
       </c>
       <c r="V308" t="n">
-        <v>3384.472909494182</v>
+        <v>3248.650778438154</v>
       </c>
       <c r="W308" t="inlineStr">
         <is>
@@ -30024,13 +30024,13 @@
       </c>
       <c r="O309" t="inlineStr"/>
       <c r="P309" t="n">
-        <v>477972.58</v>
+        <v>464467.54</v>
       </c>
       <c r="Q309" t="n">
-        <v>59746.58</v>
+        <v>58058.45</v>
       </c>
       <c r="R309" t="n">
-        <v>3366.004084507043</v>
+        <v>3270.898169014084</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -30039,10 +30039,10 @@
       </c>
       <c r="T309" t="inlineStr"/>
       <c r="U309" t="n">
-        <v>12.50000156912767</v>
+        <v>12.50000161475224</v>
       </c>
       <c r="V309" t="n">
-        <v>3366.004084507043</v>
+        <v>3270.898169014084</v>
       </c>
       <c r="W309" t="inlineStr">
         <is>
@@ -30116,13 +30116,13 @@
       </c>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="n">
-        <v>672058117.0599999</v>
+        <v>653079540.12</v>
       </c>
       <c r="Q310" t="n">
-        <v>84007264.62</v>
+        <v>81634942.52</v>
       </c>
       <c r="R310" t="n">
-        <v>3371.991395442184</v>
+        <v>3276.768085857927</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -30131,10 +30131,10 @@
       </c>
       <c r="T310" t="inlineStr"/>
       <c r="U310" t="n">
-        <v>12.49999999814004</v>
+        <v>12.5000000007656</v>
       </c>
       <c r="V310" t="n">
-        <v>3371.991395442184</v>
+        <v>3276.768085857927</v>
       </c>
       <c r="W310" t="inlineStr">
         <is>
@@ -30208,13 +30208,13 @@
       </c>
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="n">
-        <v>3578136.77</v>
+        <v>3477072.1</v>
       </c>
       <c r="Q311" t="n">
-        <v>178906.84</v>
+        <v>173853.6</v>
       </c>
       <c r="R311" t="n">
-        <v>3372.419198868991</v>
+        <v>3277.165032987748</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -30223,10 +30223,10 @@
       </c>
       <c r="T311" t="inlineStr"/>
       <c r="U311" t="n">
-        <v>5.000000041921259</v>
+        <v>4.999999856200853</v>
       </c>
       <c r="V311" t="n">
-        <v>3372.419198868991</v>
+        <v>3277.165032987748</v>
       </c>
       <c r="W311" t="inlineStr">
         <is>
@@ -30484,13 +30484,13 @@
       </c>
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="n">
-        <v>1870778727.16</v>
+        <v>1765780559.43</v>
       </c>
       <c r="Q314" t="n">
-        <v>233847340.89</v>
+        <v>220722569.93</v>
       </c>
       <c r="R314" t="n">
-        <v>3463.26345604597</v>
+        <v>3268.886477105695</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
@@ -30499,10 +30499,10 @@
       </c>
       <c r="T314" t="inlineStr"/>
       <c r="U314" t="n">
-        <v>12.49999999973273</v>
+        <v>12.50000000007079</v>
       </c>
       <c r="V314" t="n">
-        <v>3463.26345604597</v>
+        <v>3268.886477105695</v>
       </c>
       <c r="W314" t="inlineStr">
         <is>
@@ -30576,13 +30576,13 @@
       </c>
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="n">
-        <v>420067512.31</v>
+        <v>408207152.19</v>
       </c>
       <c r="Q315" t="n">
-        <v>52508439.04</v>
+        <v>51025894.02</v>
       </c>
       <c r="R315" t="n">
-        <v>3373.331772561553</v>
+        <v>3278.087726177666</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -30591,10 +30591,10 @@
       </c>
       <c r="T315" t="inlineStr"/>
       <c r="U315" t="n">
-        <v>12.50000000029757</v>
+        <v>12.49999999908135</v>
       </c>
       <c r="V315" t="n">
-        <v>3373.331772561553</v>
+        <v>3278.087726177666</v>
       </c>
       <c r="W315" t="inlineStr">
         <is>
@@ -30668,13 +30668,13 @@
       </c>
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="n">
-        <v>598550286.8200001</v>
+        <v>581639588.8</v>
       </c>
       <c r="Q316" t="n">
-        <v>74818785.86</v>
+        <v>72704948.59999999</v>
       </c>
       <c r="R316" t="n">
-        <v>3372.475289298573</v>
+        <v>3277.193551985846</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -30683,10 +30683,10 @@
       </c>
       <c r="T316" t="inlineStr"/>
       <c r="U316" t="n">
-        <v>12.50000000125303</v>
+        <v>12.5</v>
       </c>
       <c r="V316" t="n">
-        <v>3372.475289298573</v>
+        <v>3277.193551985846</v>
       </c>
       <c r="W316" t="inlineStr">
         <is>
@@ -30946,13 +30946,13 @@
       </c>
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="n">
-        <v>1323242615.4</v>
+        <v>1490889360.41</v>
       </c>
       <c r="Q319" t="n">
-        <v>492246252.93</v>
+        <v>554610842.08</v>
       </c>
       <c r="R319" t="n">
-        <v>2889.321113068997</v>
+        <v>3255.380423929586</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
@@ -30961,10 +30961,10 @@
       </c>
       <c r="T319" t="inlineStr"/>
       <c r="U319" t="n">
-        <v>37.20000000009068</v>
+        <v>37.20000000050172</v>
       </c>
       <c r="V319" t="n">
-        <v>2889.321113068997</v>
+        <v>3255.380423929586</v>
       </c>
       <c r="W319" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>1841101559.53</v>
       </c>
       <c r="Q448" t="n">
-        <v>684889780.1799999</v>
+        <v>684889772.3099999</v>
       </c>
       <c r="R448" t="n">
         <v>2615.156502346551</v>
@@ -43263,7 +43263,7 @@
       </c>
       <c r="T448" t="inlineStr"/>
       <c r="U448" t="n">
-        <v>37.20000000189234</v>
+        <v>37.19999957443086</v>
       </c>
       <c r="V448" t="n">
         <v>2615.156502346551</v>
@@ -43344,13 +43344,13 @@
       </c>
       <c r="O449" t="inlineStr"/>
       <c r="P449" t="n">
-        <v>1884080051.17</v>
+        <v>2106751373.68</v>
       </c>
       <c r="Q449" t="n">
-        <v>715950419.4299999</v>
+        <v>800565521.99</v>
       </c>
       <c r="R449" t="n">
-        <v>2615.865928919224</v>
+        <v>2925.023878731165</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
@@ -43359,10 +43359,10 @@
       </c>
       <c r="T449" t="inlineStr"/>
       <c r="U449" t="n">
-        <v>37.99999999922508</v>
+        <v>37.99999999960128</v>
       </c>
       <c r="V449" t="n">
-        <v>2615.865928919224</v>
+        <v>2925.023878731165</v>
       </c>
       <c r="W449" t="inlineStr">
         <is>

--- a/output/petroleum_sale_flat_table.xlsx
+++ b/output/petroleum_sale_flat_table.xlsx
@@ -28329,7 +28329,7 @@
         <v>4825970.67</v>
       </c>
       <c r="Q292" t="n">
-        <v>241298.53</v>
+        <v>241298.54</v>
       </c>
       <c r="R292" t="n">
         <v>230.3456002100138</v>
@@ -28343,7 +28343,7 @@
         <v>225696.1580911582</v>
       </c>
       <c r="U292" t="n">
-        <v>4.999999927475731</v>
+        <v>5.00000013468793</v>
       </c>
       <c r="V292" t="n">
         <v>230.3456002100138</v>
@@ -29537,7 +29537,7 @@
         <v>2877790983.24</v>
       </c>
       <c r="Q304" t="n">
-        <v>359723872.9</v>
+        <v>359723872.91</v>
       </c>
       <c r="R304" t="n">
         <v>256.0695</v>
@@ -29551,7 +29551,7 @@
         <v>249689.7074852225</v>
       </c>
       <c r="U304" t="n">
-        <v>12.49999999982626</v>
+        <v>12.50000000017375</v>
       </c>
       <c r="V304" t="n">
         <v>256.0695</v>
@@ -29737,7 +29737,7 @@
         <v>620186409.3200001</v>
       </c>
       <c r="Q306" t="n">
-        <v>77523301.16</v>
+        <v>77523301.17</v>
       </c>
       <c r="R306" t="n">
         <v>230.3456000017828</v>
@@ -29751,7 +29751,7 @@
         <v>225494.0414093505</v>
       </c>
       <c r="U306" t="n">
-        <v>12.49999999919379</v>
+        <v>12.50000000080621</v>
       </c>
       <c r="V306" t="n">
         <v>230.3456000017828</v>
@@ -29928,13 +29928,13 @@
       </c>
       <c r="O308" t="inlineStr"/>
       <c r="P308" t="n">
-        <v>1961197480.34</v>
+        <v>2043192757.57</v>
       </c>
       <c r="Q308" t="n">
-        <v>729565462.55</v>
+        <v>760067706.17</v>
       </c>
       <c r="R308" t="n">
-        <v>3248.650778438154</v>
+        <v>3384.472909494182</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -29943,10 +29943,10 @@
       </c>
       <c r="T308" t="inlineStr"/>
       <c r="U308" t="n">
-        <v>37.19999999304098</v>
+        <v>37.20000001732387</v>
       </c>
       <c r="V308" t="n">
-        <v>3248.650778438154</v>
+        <v>3384.472909494182</v>
       </c>
       <c r="W308" t="inlineStr">
         <is>
@@ -30024,13 +30024,13 @@
       </c>
       <c r="O309" t="inlineStr"/>
       <c r="P309" t="n">
-        <v>464467.54</v>
+        <v>477972.58</v>
       </c>
       <c r="Q309" t="n">
-        <v>58058.45</v>
+        <v>59746.58</v>
       </c>
       <c r="R309" t="n">
-        <v>3270.898169014084</v>
+        <v>3366.004084507043</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -30039,10 +30039,10 @@
       </c>
       <c r="T309" t="inlineStr"/>
       <c r="U309" t="n">
-        <v>12.50000161475224</v>
+        <v>12.50000156912767</v>
       </c>
       <c r="V309" t="n">
-        <v>3270.898169014084</v>
+        <v>3366.004084507043</v>
       </c>
       <c r="W309" t="inlineStr">
         <is>
@@ -30116,13 +30116,13 @@
       </c>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="n">
-        <v>653079540.12</v>
+        <v>672058117.0599999</v>
       </c>
       <c r="Q310" t="n">
-        <v>81634942.52</v>
+        <v>84007264.62</v>
       </c>
       <c r="R310" t="n">
-        <v>3276.768085857927</v>
+        <v>3371.991395442184</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -30131,10 +30131,10 @@
       </c>
       <c r="T310" t="inlineStr"/>
       <c r="U310" t="n">
-        <v>12.5000000007656</v>
+        <v>12.49999999814004</v>
       </c>
       <c r="V310" t="n">
-        <v>3276.768085857927</v>
+        <v>3371.991395442184</v>
       </c>
       <c r="W310" t="inlineStr">
         <is>
@@ -30208,13 +30208,13 @@
       </c>
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="n">
-        <v>3477072.1</v>
+        <v>3578136.77</v>
       </c>
       <c r="Q311" t="n">
-        <v>173853.6</v>
+        <v>178906.84</v>
       </c>
       <c r="R311" t="n">
-        <v>3277.165032987748</v>
+        <v>3372.419198868991</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -30223,10 +30223,10 @@
       </c>
       <c r="T311" t="inlineStr"/>
       <c r="U311" t="n">
-        <v>4.999999856200853</v>
+        <v>5.000000041921259</v>
       </c>
       <c r="V311" t="n">
-        <v>3277.165032987748</v>
+        <v>3372.419198868991</v>
       </c>
       <c r="W311" t="inlineStr">
         <is>
@@ -30484,13 +30484,13 @@
       </c>
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="n">
-        <v>1765780559.43</v>
+        <v>1870778727.16</v>
       </c>
       <c r="Q314" t="n">
-        <v>220722569.93</v>
+        <v>233847340.89</v>
       </c>
       <c r="R314" t="n">
-        <v>3268.886477105695</v>
+        <v>3463.26345604597</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
@@ -30499,10 +30499,10 @@
       </c>
       <c r="T314" t="inlineStr"/>
       <c r="U314" t="n">
-        <v>12.50000000007079</v>
+        <v>12.49999999973273</v>
       </c>
       <c r="V314" t="n">
-        <v>3268.886477105695</v>
+        <v>3463.26345604597</v>
       </c>
       <c r="W314" t="inlineStr">
         <is>
@@ -30576,13 +30576,13 @@
       </c>
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="n">
-        <v>408207152.19</v>
+        <v>420067512.31</v>
       </c>
       <c r="Q315" t="n">
-        <v>51025894.02</v>
+        <v>52508439.04</v>
       </c>
       <c r="R315" t="n">
-        <v>3278.087726177666</v>
+        <v>3373.331772561553</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -30591,10 +30591,10 @@
       </c>
       <c r="T315" t="inlineStr"/>
       <c r="U315" t="n">
-        <v>12.49999999908135</v>
+        <v>12.50000000029757</v>
       </c>
       <c r="V315" t="n">
-        <v>3278.087726177666</v>
+        <v>3373.331772561553</v>
       </c>
       <c r="W315" t="inlineStr">
         <is>
@@ -30668,13 +30668,13 @@
       </c>
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="n">
-        <v>581639588.8</v>
+        <v>598550286.8200001</v>
       </c>
       <c r="Q316" t="n">
-        <v>72704948.59999999</v>
+        <v>74818785.86</v>
       </c>
       <c r="R316" t="n">
-        <v>3277.193551985846</v>
+        <v>3372.475289298573</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -30683,10 +30683,10 @@
       </c>
       <c r="T316" t="inlineStr"/>
       <c r="U316" t="n">
-        <v>12.5</v>
+        <v>12.50000000125303</v>
       </c>
       <c r="V316" t="n">
-        <v>3277.193551985846</v>
+        <v>3372.475289298573</v>
       </c>
       <c r="W316" t="inlineStr">
         <is>
@@ -30946,13 +30946,13 @@
       </c>
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="n">
-        <v>1490889360.41</v>
+        <v>1323242615.4</v>
       </c>
       <c r="Q319" t="n">
-        <v>554610842.08</v>
+        <v>492246252.93</v>
       </c>
       <c r="R319" t="n">
-        <v>3255.380423929586</v>
+        <v>2889.321113068997</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
@@ -30961,10 +30961,10 @@
       </c>
       <c r="T319" t="inlineStr"/>
       <c r="U319" t="n">
-        <v>37.20000000050172</v>
+        <v>37.20000000009068</v>
       </c>
       <c r="V319" t="n">
-        <v>3255.380423929586</v>
+        <v>2889.321113068997</v>
       </c>
       <c r="W319" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>1841101559.53</v>
       </c>
       <c r="Q448" t="n">
-        <v>684889772.3099999</v>
+        <v>684889780.1799999</v>
       </c>
       <c r="R448" t="n">
         <v>2615.156502346551</v>
@@ -43263,7 +43263,7 @@
       </c>
       <c r="T448" t="inlineStr"/>
       <c r="U448" t="n">
-        <v>37.19999957443086</v>
+        <v>37.20000000189234</v>
       </c>
       <c r="V448" t="n">
         <v>2615.156502346551</v>
@@ -43344,13 +43344,13 @@
       </c>
       <c r="O449" t="inlineStr"/>
       <c r="P449" t="n">
-        <v>2106751373.68</v>
+        <v>1884080051.17</v>
       </c>
       <c r="Q449" t="n">
-        <v>800565521.99</v>
+        <v>715950419.4299999</v>
       </c>
       <c r="R449" t="n">
-        <v>2925.023878731165</v>
+        <v>2615.865928919224</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
@@ -43359,10 +43359,10 @@
       </c>
       <c r="T449" t="inlineStr"/>
       <c r="U449" t="n">
-        <v>37.99999999960128</v>
+        <v>37.99999999922508</v>
       </c>
       <c r="V449" t="n">
-        <v>2925.023878731165</v>
+        <v>2615.865928919224</v>
       </c>
       <c r="W449" t="inlineStr">
         <is>
